--- a/excel/月次予算割振.xlsx
+++ b/excel/月次予算割振.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]-#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="#,##0.##;[Red]-#,##0.##;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,11 @@
       <name val="Meiryo UI"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <color rgb="000000FF"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -123,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,6 +183,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1874,21 +1880,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1936,46 +1943,51 @@
           <t>月予算</t>
         </is>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>割振方法</t>
+        </is>
+      </c>
+      <c r="D6" s="9">
         <f>設定!$B$21</f>
         <v/>
       </c>
-      <c r="D6" s="9">
+      <c r="E6" s="9">
         <f>設定!$B$22</f>
         <v/>
       </c>
-      <c r="E6" s="9">
+      <c r="F6" s="9">
         <f>設定!$B$23</f>
         <v/>
       </c>
-      <c r="F6" s="9">
+      <c r="G6" s="9">
         <f>設定!$B$24</f>
         <v/>
       </c>
-      <c r="G6" s="9">
+      <c r="H6" s="9">
         <f>設定!$B$25</f>
         <v/>
       </c>
-      <c r="H6" s="9">
+      <c r="I6" s="9">
         <f>設定!$B$26</f>
         <v/>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>配分計</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>明細合計</t>
         </is>
       </c>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>差（予算−明細）</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -1988,37 +2000,38 @@
         </is>
       </c>
       <c r="B7" s="30" t="n"/>
-      <c r="C7" s="31">
-        <f>IF(C$6="","",動員予測!$M$4)</f>
-        <v/>
-      </c>
+      <c r="C7" s="30" t="n"/>
       <c r="D7" s="31">
-        <f>IF(D$6="","",動員予測!$M$5)</f>
+        <f>IF(D$6="","",動員予測!$M$4)</f>
         <v/>
       </c>
       <c r="E7" s="31">
-        <f>IF(E$6="","",動員予測!$M$6)</f>
+        <f>IF(E$6="","",動員予測!$M$5)</f>
         <v/>
       </c>
       <c r="F7" s="31">
-        <f>IF(F$6="","",動員予測!$M$7)</f>
+        <f>IF(F$6="","",動員予測!$M$6)</f>
         <v/>
       </c>
       <c r="G7" s="31">
-        <f>IF(G$6="","",動員予測!$M$8)</f>
+        <f>IF(G$6="","",動員予測!$M$7)</f>
         <v/>
       </c>
       <c r="H7" s="31">
-        <f>IF(H$6="","",動員予測!$M$9)</f>
+        <f>IF(H$6="","",動員予測!$M$8)</f>
         <v/>
       </c>
       <c r="I7" s="31">
-        <f>IF($B$4=0,"",SUM($C7:$H7))</f>
-        <v/>
-      </c>
-      <c r="J7" s="30" t="n"/>
+        <f>IF(I$6="","",動員予測!$M$9)</f>
+        <v/>
+      </c>
+      <c r="J7" s="31">
+        <f>IF($B$4=0,"",SUM(D7:I7))</f>
+        <v/>
+      </c>
       <c r="K7" s="30" t="n"/>
       <c r="L7" s="30" t="n"/>
+      <c r="M7" s="30" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -2027,43 +2040,48 @@
         </is>
       </c>
       <c r="B8" s="18" t="n"/>
-      <c r="C8" s="20">
-        <f>IF(OR($A8="",C$6=""),"",IF(D$6="",$B8,ROUND($B8*C$7,0)))</f>
-        <v/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D8" s="20">
-        <f>IF(OR($A8="",D$6=""),"",IF(E$6="",$B8-SUM($C8:C8),ROUND($B8*D$7,0)))</f>
+        <f>IF(OR($A8="",D$6=""),"",IF(E$6="",$B8,IF($C8="最終週",0,IF($C8="均等",ROUND($B8/$D$4,0),ROUND($B8*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E8" s="20">
-        <f>IF(OR($A8="",E$6=""),"",IF(F$6="",$B8-SUM($C8:D8),ROUND($B8*E$7,0)))</f>
+        <f>IF(OR($A8="",E$6=""),"",IF(F$6="",$B8-SUM($D8:D8),IF($C8="最終週",0,IF($C8="均等",ROUND($B8/$D$4,0),ROUND($B8*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F8" s="20">
-        <f>IF(OR($A8="",F$6=""),"",IF(G$6="",$B8-SUM($C8:E8),ROUND($B8*F$7,0)))</f>
+        <f>IF(OR($A8="",F$6=""),"",IF(G$6="",$B8-SUM($D8:E8),IF($C8="最終週",0,IF($C8="均等",ROUND($B8/$D$4,0),ROUND($B8*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G8" s="20">
-        <f>IF(OR($A8="",G$6=""),"",IF(H$6="",$B8-SUM($C8:F8),ROUND($B8*G$7,0)))</f>
+        <f>IF(OR($A8="",G$6=""),"",IF(H$6="",$B8-SUM($D8:F8),IF($C8="最終週",0,IF($C8="均等",ROUND($B8/$D$4,0),ROUND($B8*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H8" s="20">
-        <f>IF(OR($A8="",H$6=""),"",$B8-SUM($C8:G8))</f>
-        <v/>
-      </c>
-      <c r="I8" s="21">
-        <f>IF($A8="","",SUM($C8:$H8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="20">
+        <f>IF(OR($A8="",H$6=""),"",IF(I$6="",$B8-SUM($D8:G8),IF($C8="最終週",0,IF($C8="均等",ROUND($B8/$D$4,0),ROUND($B8*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I8" s="20">
+        <f>IF(OR($A8="",I$6=""),"",$B8-SUM($D8:H8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="21">
+        <f>IF($A8="","",SUM(D8:I8))</f>
+        <v/>
+      </c>
+      <c r="K8" s="20">
         <f>IF($A8="","",SUMIF(明細!$A$5:$A$104,$A8,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K8" s="20">
-        <f>IF(OR($A8="",$J8=0),"",$B8-$J8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="20">
+        <f>IF(OR($A8="",K8=0),"",$B8-K8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="32" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -2072,43 +2090,48 @@
         </is>
       </c>
       <c r="B9" s="18" t="n"/>
-      <c r="C9" s="20">
-        <f>IF(OR($A9="",C$6=""),"",IF(D$6="",$B9,ROUND($B9*C$7,0)))</f>
-        <v/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D9" s="20">
-        <f>IF(OR($A9="",D$6=""),"",IF(E$6="",$B9-SUM($C9:C9),ROUND($B9*D$7,0)))</f>
+        <f>IF(OR($A9="",D$6=""),"",IF(E$6="",$B9,IF($C9="最終週",0,IF($C9="均等",ROUND($B9/$D$4,0),ROUND($B9*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E9" s="20">
-        <f>IF(OR($A9="",E$6=""),"",IF(F$6="",$B9-SUM($C9:D9),ROUND($B9*E$7,0)))</f>
+        <f>IF(OR($A9="",E$6=""),"",IF(F$6="",$B9-SUM($D9:D9),IF($C9="最終週",0,IF($C9="均等",ROUND($B9/$D$4,0),ROUND($B9*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F9" s="20">
-        <f>IF(OR($A9="",F$6=""),"",IF(G$6="",$B9-SUM($C9:E9),ROUND($B9*F$7,0)))</f>
+        <f>IF(OR($A9="",F$6=""),"",IF(G$6="",$B9-SUM($D9:E9),IF($C9="最終週",0,IF($C9="均等",ROUND($B9/$D$4,0),ROUND($B9*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G9" s="20">
-        <f>IF(OR($A9="",G$6=""),"",IF(H$6="",$B9-SUM($C9:F9),ROUND($B9*G$7,0)))</f>
+        <f>IF(OR($A9="",G$6=""),"",IF(H$6="",$B9-SUM($D9:F9),IF($C9="最終週",0,IF($C9="均等",ROUND($B9/$D$4,0),ROUND($B9*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H9" s="20">
-        <f>IF(OR($A9="",H$6=""),"",$B9-SUM($C9:G9))</f>
-        <v/>
-      </c>
-      <c r="I9" s="21">
-        <f>IF($A9="","",SUM($C9:$H9))</f>
-        <v/>
-      </c>
-      <c r="J9" s="20">
+        <f>IF(OR($A9="",H$6=""),"",IF(I$6="",$B9-SUM($D9:G9),IF($C9="最終週",0,IF($C9="均等",ROUND($B9/$D$4,0),ROUND($B9*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I9" s="20">
+        <f>IF(OR($A9="",I$6=""),"",$B9-SUM($D9:H9))</f>
+        <v/>
+      </c>
+      <c r="J9" s="21">
+        <f>IF($A9="","",SUM(D9:I9))</f>
+        <v/>
+      </c>
+      <c r="K9" s="20">
         <f>IF($A9="","",SUMIF(明細!$A$5:$A$104,$A9,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K9" s="20">
-        <f>IF(OR($A9="",$J9=0),"",$B9-$J9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="20">
+        <f>IF(OR($A9="",K9=0),"",$B9-K9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="32" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -2117,43 +2140,48 @@
         </is>
       </c>
       <c r="B10" s="18" t="n"/>
-      <c r="C10" s="20">
-        <f>IF(OR($A10="",C$6=""),"",IF(D$6="",$B10,ROUND($B10*C$7,0)))</f>
-        <v/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D10" s="20">
-        <f>IF(OR($A10="",D$6=""),"",IF(E$6="",$B10-SUM($C10:C10),ROUND($B10*D$7,0)))</f>
+        <f>IF(OR($A10="",D$6=""),"",IF(E$6="",$B10,IF($C10="最終週",0,IF($C10="均等",ROUND($B10/$D$4,0),ROUND($B10*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E10" s="20">
-        <f>IF(OR($A10="",E$6=""),"",IF(F$6="",$B10-SUM($C10:D10),ROUND($B10*E$7,0)))</f>
+        <f>IF(OR($A10="",E$6=""),"",IF(F$6="",$B10-SUM($D10:D10),IF($C10="最終週",0,IF($C10="均等",ROUND($B10/$D$4,0),ROUND($B10*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F10" s="20">
-        <f>IF(OR($A10="",F$6=""),"",IF(G$6="",$B10-SUM($C10:E10),ROUND($B10*F$7,0)))</f>
+        <f>IF(OR($A10="",F$6=""),"",IF(G$6="",$B10-SUM($D10:E10),IF($C10="最終週",0,IF($C10="均等",ROUND($B10/$D$4,0),ROUND($B10*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G10" s="20">
-        <f>IF(OR($A10="",G$6=""),"",IF(H$6="",$B10-SUM($C10:F10),ROUND($B10*G$7,0)))</f>
+        <f>IF(OR($A10="",G$6=""),"",IF(H$6="",$B10-SUM($D10:F10),IF($C10="最終週",0,IF($C10="均等",ROUND($B10/$D$4,0),ROUND($B10*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H10" s="20">
-        <f>IF(OR($A10="",H$6=""),"",$B10-SUM($C10:G10))</f>
-        <v/>
-      </c>
-      <c r="I10" s="21">
-        <f>IF($A10="","",SUM($C10:$H10))</f>
-        <v/>
-      </c>
-      <c r="J10" s="20">
+        <f>IF(OR($A10="",H$6=""),"",IF(I$6="",$B10-SUM($D10:G10),IF($C10="最終週",0,IF($C10="均等",ROUND($B10/$D$4,0),ROUND($B10*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I10" s="20">
+        <f>IF(OR($A10="",I$6=""),"",$B10-SUM($D10:H10))</f>
+        <v/>
+      </c>
+      <c r="J10" s="21">
+        <f>IF($A10="","",SUM(D10:I10))</f>
+        <v/>
+      </c>
+      <c r="K10" s="20">
         <f>IF($A10="","",SUMIF(明細!$A$5:$A$104,$A10,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K10" s="20">
-        <f>IF(OR($A10="",$J10=0),"",$B10-$J10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="20">
+        <f>IF(OR($A10="",K10=0),"",$B10-K10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="32" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -2162,43 +2190,48 @@
         </is>
       </c>
       <c r="B11" s="18" t="n"/>
-      <c r="C11" s="20">
-        <f>IF(OR($A11="",C$6=""),"",IF(D$6="",$B11,ROUND($B11*C$7,0)))</f>
-        <v/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D11" s="20">
-        <f>IF(OR($A11="",D$6=""),"",IF(E$6="",$B11-SUM($C11:C11),ROUND($B11*D$7,0)))</f>
+        <f>IF(OR($A11="",D$6=""),"",IF(E$6="",$B11,IF($C11="最終週",0,IF($C11="均等",ROUND($B11/$D$4,0),ROUND($B11*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E11" s="20">
-        <f>IF(OR($A11="",E$6=""),"",IF(F$6="",$B11-SUM($C11:D11),ROUND($B11*E$7,0)))</f>
+        <f>IF(OR($A11="",E$6=""),"",IF(F$6="",$B11-SUM($D11:D11),IF($C11="最終週",0,IF($C11="均等",ROUND($B11/$D$4,0),ROUND($B11*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F11" s="20">
-        <f>IF(OR($A11="",F$6=""),"",IF(G$6="",$B11-SUM($C11:E11),ROUND($B11*F$7,0)))</f>
+        <f>IF(OR($A11="",F$6=""),"",IF(G$6="",$B11-SUM($D11:E11),IF($C11="最終週",0,IF($C11="均等",ROUND($B11/$D$4,0),ROUND($B11*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G11" s="20">
-        <f>IF(OR($A11="",G$6=""),"",IF(H$6="",$B11-SUM($C11:F11),ROUND($B11*G$7,0)))</f>
+        <f>IF(OR($A11="",G$6=""),"",IF(H$6="",$B11-SUM($D11:F11),IF($C11="最終週",0,IF($C11="均等",ROUND($B11/$D$4,0),ROUND($B11*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H11" s="20">
-        <f>IF(OR($A11="",H$6=""),"",$B11-SUM($C11:G11))</f>
-        <v/>
-      </c>
-      <c r="I11" s="21">
-        <f>IF($A11="","",SUM($C11:$H11))</f>
-        <v/>
-      </c>
-      <c r="J11" s="20">
+        <f>IF(OR($A11="",H$6=""),"",IF(I$6="",$B11-SUM($D11:G11),IF($C11="最終週",0,IF($C11="均等",ROUND($B11/$D$4,0),ROUND($B11*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I11" s="20">
+        <f>IF(OR($A11="",I$6=""),"",$B11-SUM($D11:H11))</f>
+        <v/>
+      </c>
+      <c r="J11" s="21">
+        <f>IF($A11="","",SUM(D11:I11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="20">
         <f>IF($A11="","",SUMIF(明細!$A$5:$A$104,$A11,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K11" s="20">
-        <f>IF(OR($A11="",$J11=0),"",$B11-$J11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="20">
+        <f>IF(OR($A11="",K11=0),"",$B11-K11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="32" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -2207,43 +2240,48 @@
         </is>
       </c>
       <c r="B12" s="18" t="n"/>
-      <c r="C12" s="20">
-        <f>IF(OR($A12="",C$6=""),"",IF(D$6="",$B12,ROUND($B12*C$7,0)))</f>
-        <v/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D12" s="20">
-        <f>IF(OR($A12="",D$6=""),"",IF(E$6="",$B12-SUM($C12:C12),ROUND($B12*D$7,0)))</f>
+        <f>IF(OR($A12="",D$6=""),"",IF(E$6="",$B12,IF($C12="最終週",0,IF($C12="均等",ROUND($B12/$D$4,0),ROUND($B12*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E12" s="20">
-        <f>IF(OR($A12="",E$6=""),"",IF(F$6="",$B12-SUM($C12:D12),ROUND($B12*E$7,0)))</f>
+        <f>IF(OR($A12="",E$6=""),"",IF(F$6="",$B12-SUM($D12:D12),IF($C12="最終週",0,IF($C12="均等",ROUND($B12/$D$4,0),ROUND($B12*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F12" s="20">
-        <f>IF(OR($A12="",F$6=""),"",IF(G$6="",$B12-SUM($C12:E12),ROUND($B12*F$7,0)))</f>
+        <f>IF(OR($A12="",F$6=""),"",IF(G$6="",$B12-SUM($D12:E12),IF($C12="最終週",0,IF($C12="均等",ROUND($B12/$D$4,0),ROUND($B12*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G12" s="20">
-        <f>IF(OR($A12="",G$6=""),"",IF(H$6="",$B12-SUM($C12:F12),ROUND($B12*G$7,0)))</f>
+        <f>IF(OR($A12="",G$6=""),"",IF(H$6="",$B12-SUM($D12:F12),IF($C12="最終週",0,IF($C12="均等",ROUND($B12/$D$4,0),ROUND($B12*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H12" s="20">
-        <f>IF(OR($A12="",H$6=""),"",$B12-SUM($C12:G12))</f>
-        <v/>
-      </c>
-      <c r="I12" s="21">
-        <f>IF($A12="","",SUM($C12:$H12))</f>
-        <v/>
-      </c>
-      <c r="J12" s="20">
+        <f>IF(OR($A12="",H$6=""),"",IF(I$6="",$B12-SUM($D12:G12),IF($C12="最終週",0,IF($C12="均等",ROUND($B12/$D$4,0),ROUND($B12*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I12" s="20">
+        <f>IF(OR($A12="",I$6=""),"",$B12-SUM($D12:H12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="21">
+        <f>IF($A12="","",SUM(D12:I12))</f>
+        <v/>
+      </c>
+      <c r="K12" s="20">
         <f>IF($A12="","",SUMIF(明細!$A$5:$A$104,$A12,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K12" s="20">
-        <f>IF(OR($A12="",$J12=0),"",$B12-$J12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="20">
+        <f>IF(OR($A12="",K12=0),"",$B12-K12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="32" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -2252,43 +2290,48 @@
         </is>
       </c>
       <c r="B13" s="18" t="n"/>
-      <c r="C13" s="20">
-        <f>IF(OR($A13="",C$6=""),"",IF(D$6="",$B13,ROUND($B13*C$7,0)))</f>
-        <v/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D13" s="20">
-        <f>IF(OR($A13="",D$6=""),"",IF(E$6="",$B13-SUM($C13:C13),ROUND($B13*D$7,0)))</f>
+        <f>IF(OR($A13="",D$6=""),"",IF(E$6="",$B13,IF($C13="最終週",0,IF($C13="均等",ROUND($B13/$D$4,0),ROUND($B13*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E13" s="20">
-        <f>IF(OR($A13="",E$6=""),"",IF(F$6="",$B13-SUM($C13:D13),ROUND($B13*E$7,0)))</f>
+        <f>IF(OR($A13="",E$6=""),"",IF(F$6="",$B13-SUM($D13:D13),IF($C13="最終週",0,IF($C13="均等",ROUND($B13/$D$4,0),ROUND($B13*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F13" s="20">
-        <f>IF(OR($A13="",F$6=""),"",IF(G$6="",$B13-SUM($C13:E13),ROUND($B13*F$7,0)))</f>
+        <f>IF(OR($A13="",F$6=""),"",IF(G$6="",$B13-SUM($D13:E13),IF($C13="最終週",0,IF($C13="均等",ROUND($B13/$D$4,0),ROUND($B13*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G13" s="20">
-        <f>IF(OR($A13="",G$6=""),"",IF(H$6="",$B13-SUM($C13:F13),ROUND($B13*G$7,0)))</f>
+        <f>IF(OR($A13="",G$6=""),"",IF(H$6="",$B13-SUM($D13:F13),IF($C13="最終週",0,IF($C13="均等",ROUND($B13/$D$4,0),ROUND($B13*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H13" s="20">
-        <f>IF(OR($A13="",H$6=""),"",$B13-SUM($C13:G13))</f>
-        <v/>
-      </c>
-      <c r="I13" s="21">
-        <f>IF($A13="","",SUM($C13:$H13))</f>
-        <v/>
-      </c>
-      <c r="J13" s="20">
+        <f>IF(OR($A13="",H$6=""),"",IF(I$6="",$B13-SUM($D13:G13),IF($C13="最終週",0,IF($C13="均等",ROUND($B13/$D$4,0),ROUND($B13*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I13" s="20">
+        <f>IF(OR($A13="",I$6=""),"",$B13-SUM($D13:H13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="21">
+        <f>IF($A13="","",SUM(D13:I13))</f>
+        <v/>
+      </c>
+      <c r="K13" s="20">
         <f>IF($A13="","",SUMIF(明細!$A$5:$A$104,$A13,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K13" s="20">
-        <f>IF(OR($A13="",$J13=0),"",$B13-$J13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="20">
+        <f>IF(OR($A13="",K13=0),"",$B13-K13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="32" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -2297,43 +2340,48 @@
         </is>
       </c>
       <c r="B14" s="18" t="n"/>
-      <c r="C14" s="20">
-        <f>IF(OR($A14="",C$6=""),"",IF(D$6="",$B14,ROUND($B14*C$7,0)))</f>
-        <v/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D14" s="20">
-        <f>IF(OR($A14="",D$6=""),"",IF(E$6="",$B14-SUM($C14:C14),ROUND($B14*D$7,0)))</f>
+        <f>IF(OR($A14="",D$6=""),"",IF(E$6="",$B14,IF($C14="最終週",0,IF($C14="均等",ROUND($B14/$D$4,0),ROUND($B14*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E14" s="20">
-        <f>IF(OR($A14="",E$6=""),"",IF(F$6="",$B14-SUM($C14:D14),ROUND($B14*E$7,0)))</f>
+        <f>IF(OR($A14="",E$6=""),"",IF(F$6="",$B14-SUM($D14:D14),IF($C14="最終週",0,IF($C14="均等",ROUND($B14/$D$4,0),ROUND($B14*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F14" s="20">
-        <f>IF(OR($A14="",F$6=""),"",IF(G$6="",$B14-SUM($C14:E14),ROUND($B14*F$7,0)))</f>
+        <f>IF(OR($A14="",F$6=""),"",IF(G$6="",$B14-SUM($D14:E14),IF($C14="最終週",0,IF($C14="均等",ROUND($B14/$D$4,0),ROUND($B14*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G14" s="20">
-        <f>IF(OR($A14="",G$6=""),"",IF(H$6="",$B14-SUM($C14:F14),ROUND($B14*G$7,0)))</f>
+        <f>IF(OR($A14="",G$6=""),"",IF(H$6="",$B14-SUM($D14:F14),IF($C14="最終週",0,IF($C14="均等",ROUND($B14/$D$4,0),ROUND($B14*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H14" s="20">
-        <f>IF(OR($A14="",H$6=""),"",$B14-SUM($C14:G14))</f>
-        <v/>
-      </c>
-      <c r="I14" s="21">
-        <f>IF($A14="","",SUM($C14:$H14))</f>
-        <v/>
-      </c>
-      <c r="J14" s="20">
+        <f>IF(OR($A14="",H$6=""),"",IF(I$6="",$B14-SUM($D14:G14),IF($C14="最終週",0,IF($C14="均等",ROUND($B14/$D$4,0),ROUND($B14*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I14" s="20">
+        <f>IF(OR($A14="",I$6=""),"",$B14-SUM($D14:H14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="21">
+        <f>IF($A14="","",SUM(D14:I14))</f>
+        <v/>
+      </c>
+      <c r="K14" s="20">
         <f>IF($A14="","",SUMIF(明細!$A$5:$A$104,$A14,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K14" s="20">
-        <f>IF(OR($A14="",$J14=0),"",$B14-$J14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="20">
+        <f>IF(OR($A14="",K14=0),"",$B14-K14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="32" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -2342,43 +2390,48 @@
         </is>
       </c>
       <c r="B15" s="18" t="n"/>
-      <c r="C15" s="20">
-        <f>IF(OR($A15="",C$6=""),"",IF(D$6="",$B15,ROUND($B15*C$7,0)))</f>
-        <v/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D15" s="20">
-        <f>IF(OR($A15="",D$6=""),"",IF(E$6="",$B15-SUM($C15:C15),ROUND($B15*D$7,0)))</f>
+        <f>IF(OR($A15="",D$6=""),"",IF(E$6="",$B15,IF($C15="最終週",0,IF($C15="均等",ROUND($B15/$D$4,0),ROUND($B15*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E15" s="20">
-        <f>IF(OR($A15="",E$6=""),"",IF(F$6="",$B15-SUM($C15:D15),ROUND($B15*E$7,0)))</f>
+        <f>IF(OR($A15="",E$6=""),"",IF(F$6="",$B15-SUM($D15:D15),IF($C15="最終週",0,IF($C15="均等",ROUND($B15/$D$4,0),ROUND($B15*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>IF(OR($A15="",F$6=""),"",IF(G$6="",$B15-SUM($C15:E15),ROUND($B15*F$7,0)))</f>
+        <f>IF(OR($A15="",F$6=""),"",IF(G$6="",$B15-SUM($D15:E15),IF($C15="最終週",0,IF($C15="均等",ROUND($B15/$D$4,0),ROUND($B15*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G15" s="20">
-        <f>IF(OR($A15="",G$6=""),"",IF(H$6="",$B15-SUM($C15:F15),ROUND($B15*G$7,0)))</f>
+        <f>IF(OR($A15="",G$6=""),"",IF(H$6="",$B15-SUM($D15:F15),IF($C15="最終週",0,IF($C15="均等",ROUND($B15/$D$4,0),ROUND($B15*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H15" s="20">
-        <f>IF(OR($A15="",H$6=""),"",$B15-SUM($C15:G15))</f>
-        <v/>
-      </c>
-      <c r="I15" s="21">
-        <f>IF($A15="","",SUM($C15:$H15))</f>
-        <v/>
-      </c>
-      <c r="J15" s="20">
+        <f>IF(OR($A15="",H$6=""),"",IF(I$6="",$B15-SUM($D15:G15),IF($C15="最終週",0,IF($C15="均等",ROUND($B15/$D$4,0),ROUND($B15*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I15" s="20">
+        <f>IF(OR($A15="",I$6=""),"",$B15-SUM($D15:H15))</f>
+        <v/>
+      </c>
+      <c r="J15" s="21">
+        <f>IF($A15="","",SUM(D15:I15))</f>
+        <v/>
+      </c>
+      <c r="K15" s="20">
         <f>IF($A15="","",SUMIF(明細!$A$5:$A$104,$A15,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K15" s="20">
-        <f>IF(OR($A15="",$J15=0),"",$B15-$J15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="20">
+        <f>IF(OR($A15="",K15=0),"",$B15-K15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="32" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -2387,43 +2440,48 @@
         </is>
       </c>
       <c r="B16" s="18" t="n"/>
-      <c r="C16" s="20">
-        <f>IF(OR($A16="",C$6=""),"",IF(D$6="",$B16,ROUND($B16*C$7,0)))</f>
-        <v/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D16" s="20">
-        <f>IF(OR($A16="",D$6=""),"",IF(E$6="",$B16-SUM($C16:C16),ROUND($B16*D$7,0)))</f>
+        <f>IF(OR($A16="",D$6=""),"",IF(E$6="",$B16,IF($C16="最終週",0,IF($C16="均等",ROUND($B16/$D$4,0),ROUND($B16*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f>IF(OR($A16="",E$6=""),"",IF(F$6="",$B16-SUM($C16:D16),ROUND($B16*E$7,0)))</f>
+        <f>IF(OR($A16="",E$6=""),"",IF(F$6="",$B16-SUM($D16:D16),IF($C16="最終週",0,IF($C16="均等",ROUND($B16/$D$4,0),ROUND($B16*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F16" s="20">
-        <f>IF(OR($A16="",F$6=""),"",IF(G$6="",$B16-SUM($C16:E16),ROUND($B16*F$7,0)))</f>
+        <f>IF(OR($A16="",F$6=""),"",IF(G$6="",$B16-SUM($D16:E16),IF($C16="最終週",0,IF($C16="均等",ROUND($B16/$D$4,0),ROUND($B16*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G16" s="20">
-        <f>IF(OR($A16="",G$6=""),"",IF(H$6="",$B16-SUM($C16:F16),ROUND($B16*G$7,0)))</f>
+        <f>IF(OR($A16="",G$6=""),"",IF(H$6="",$B16-SUM($D16:F16),IF($C16="最終週",0,IF($C16="均等",ROUND($B16/$D$4,0),ROUND($B16*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H16" s="20">
-        <f>IF(OR($A16="",H$6=""),"",$B16-SUM($C16:G16))</f>
-        <v/>
-      </c>
-      <c r="I16" s="21">
-        <f>IF($A16="","",SUM($C16:$H16))</f>
-        <v/>
-      </c>
-      <c r="J16" s="20">
+        <f>IF(OR($A16="",H$6=""),"",IF(I$6="",$B16-SUM($D16:G16),IF($C16="最終週",0,IF($C16="均等",ROUND($B16/$D$4,0),ROUND($B16*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I16" s="20">
+        <f>IF(OR($A16="",I$6=""),"",$B16-SUM($D16:H16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="21">
+        <f>IF($A16="","",SUM(D16:I16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="20">
         <f>IF($A16="","",SUMIF(明細!$A$5:$A$104,$A16,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K16" s="20">
-        <f>IF(OR($A16="",$J16=0),"",$B16-$J16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="20">
+        <f>IF(OR($A16="",K16=0),"",$B16-K16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="32" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -2432,43 +2490,48 @@
         </is>
       </c>
       <c r="B17" s="18" t="n"/>
-      <c r="C17" s="20">
-        <f>IF(OR($A17="",C$6=""),"",IF(D$6="",$B17,ROUND($B17*C$7,0)))</f>
-        <v/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D17" s="20">
-        <f>IF(OR($A17="",D$6=""),"",IF(E$6="",$B17-SUM($C17:C17),ROUND($B17*D$7,0)))</f>
+        <f>IF(OR($A17="",D$6=""),"",IF(E$6="",$B17,IF($C17="最終週",0,IF($C17="均等",ROUND($B17/$D$4,0),ROUND($B17*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E17" s="20">
-        <f>IF(OR($A17="",E$6=""),"",IF(F$6="",$B17-SUM($C17:D17),ROUND($B17*E$7,0)))</f>
+        <f>IF(OR($A17="",E$6=""),"",IF(F$6="",$B17-SUM($D17:D17),IF($C17="最終週",0,IF($C17="均等",ROUND($B17/$D$4,0),ROUND($B17*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F17" s="20">
-        <f>IF(OR($A17="",F$6=""),"",IF(G$6="",$B17-SUM($C17:E17),ROUND($B17*F$7,0)))</f>
+        <f>IF(OR($A17="",F$6=""),"",IF(G$6="",$B17-SUM($D17:E17),IF($C17="最終週",0,IF($C17="均等",ROUND($B17/$D$4,0),ROUND($B17*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G17" s="20">
-        <f>IF(OR($A17="",G$6=""),"",IF(H$6="",$B17-SUM($C17:F17),ROUND($B17*G$7,0)))</f>
+        <f>IF(OR($A17="",G$6=""),"",IF(H$6="",$B17-SUM($D17:F17),IF($C17="最終週",0,IF($C17="均等",ROUND($B17/$D$4,0),ROUND($B17*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H17" s="20">
-        <f>IF(OR($A17="",H$6=""),"",$B17-SUM($C17:G17))</f>
-        <v/>
-      </c>
-      <c r="I17" s="21">
-        <f>IF($A17="","",SUM($C17:$H17))</f>
-        <v/>
-      </c>
-      <c r="J17" s="20">
+        <f>IF(OR($A17="",H$6=""),"",IF(I$6="",$B17-SUM($D17:G17),IF($C17="最終週",0,IF($C17="均等",ROUND($B17/$D$4,0),ROUND($B17*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I17" s="20">
+        <f>IF(OR($A17="",I$6=""),"",$B17-SUM($D17:H17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="21">
+        <f>IF($A17="","",SUM(D17:I17))</f>
+        <v/>
+      </c>
+      <c r="K17" s="20">
         <f>IF($A17="","",SUMIF(明細!$A$5:$A$104,$A17,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K17" s="20">
-        <f>IF(OR($A17="",$J17=0),"",$B17-$J17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="20">
+        <f>IF(OR($A17="",K17=0),"",$B17-K17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="32" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -2477,43 +2540,52 @@
         </is>
       </c>
       <c r="B18" s="18" t="n"/>
-      <c r="C18" s="20">
-        <f>IF(OR($A18="",C$6=""),"",IF(D$6="",$B18,ROUND($B18*C$7,0)))</f>
-        <v/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>最終週</t>
+        </is>
       </c>
       <c r="D18" s="20">
-        <f>IF(OR($A18="",D$6=""),"",IF(E$6="",$B18-SUM($C18:C18),ROUND($B18*D$7,0)))</f>
+        <f>IF(OR($A18="",D$6=""),"",IF(E$6="",$B18,IF($C18="最終週",0,IF($C18="均等",ROUND($B18/$D$4,0),ROUND($B18*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E18" s="20">
-        <f>IF(OR($A18="",E$6=""),"",IF(F$6="",$B18-SUM($C18:D18),ROUND($B18*E$7,0)))</f>
+        <f>IF(OR($A18="",E$6=""),"",IF(F$6="",$B18-SUM($D18:D18),IF($C18="最終週",0,IF($C18="均等",ROUND($B18/$D$4,0),ROUND($B18*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F18" s="20">
-        <f>IF(OR($A18="",F$6=""),"",IF(G$6="",$B18-SUM($C18:E18),ROUND($B18*F$7,0)))</f>
+        <f>IF(OR($A18="",F$6=""),"",IF(G$6="",$B18-SUM($D18:E18),IF($C18="最終週",0,IF($C18="均等",ROUND($B18/$D$4,0),ROUND($B18*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G18" s="20">
-        <f>IF(OR($A18="",G$6=""),"",IF(H$6="",$B18-SUM($C18:F18),ROUND($B18*G$7,0)))</f>
+        <f>IF(OR($A18="",G$6=""),"",IF(H$6="",$B18-SUM($D18:F18),IF($C18="最終週",0,IF($C18="均等",ROUND($B18/$D$4,0),ROUND($B18*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H18" s="20">
-        <f>IF(OR($A18="",H$6=""),"",$B18-SUM($C18:G18))</f>
-        <v/>
-      </c>
-      <c r="I18" s="21">
-        <f>IF($A18="","",SUM($C18:$H18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="20">
+        <f>IF(OR($A18="",H$6=""),"",IF(I$6="",$B18-SUM($D18:G18),IF($C18="最終週",0,IF($C18="均等",ROUND($B18/$D$4,0),ROUND($B18*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I18" s="20">
+        <f>IF(OR($A18="",I$6=""),"",$B18-SUM($D18:H18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="21">
+        <f>IF($A18="","",SUM(D18:I18))</f>
+        <v/>
+      </c>
+      <c r="K18" s="20">
         <f>IF($A18="","",SUMIF(明細!$A$5:$A$104,$A18,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K18" s="20">
-        <f>IF(OR($A18="",$J18=0),"",$B18-$J18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="20">
+        <f>IF(OR($A18="",K18=0),"",$B18-K18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="32" t="inlineStr">
+        <is>
+          <t>月末の週にまとめて計上</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -2525,37 +2597,42 @@
         <f>有休!$B$5</f>
         <v/>
       </c>
-      <c r="C19" s="20">
-        <f>IF(C$6="","",有休!$E$8)</f>
-        <v/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>有休シート</t>
+        </is>
       </c>
       <c r="D19" s="20">
-        <f>IF(D$6="","",有休!$E$9)</f>
+        <f>IF(D$6="","",有休!$E$8)</f>
         <v/>
       </c>
       <c r="E19" s="20">
-        <f>IF(E$6="","",有休!$E$10)</f>
+        <f>IF(E$6="","",有休!$E$9)</f>
         <v/>
       </c>
       <c r="F19" s="20">
-        <f>IF(F$6="","",有休!$E$11)</f>
+        <f>IF(F$6="","",有休!$E$10)</f>
         <v/>
       </c>
       <c r="G19" s="20">
-        <f>IF(G$6="","",有休!$E$12)</f>
+        <f>IF(G$6="","",有休!$E$11)</f>
         <v/>
       </c>
       <c r="H19" s="20">
-        <f>IF(H$6="","",有休!$E$13)</f>
-        <v/>
-      </c>
-      <c r="I19" s="21">
-        <f>IF($A19="","",SUM($C19:$H19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="12" t="n"/>
+        <f>IF(H$6="","",有休!$E$12)</f>
+        <v/>
+      </c>
+      <c r="I19" s="20">
+        <f>IF(I$6="","",有休!$E$13)</f>
+        <v/>
+      </c>
+      <c r="J19" s="21">
+        <f>IF($A19="","",SUM(D19:I19))</f>
+        <v/>
+      </c>
       <c r="K19" s="12" t="n"/>
-      <c r="L19" s="32" t="inlineStr">
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="33" t="inlineStr">
         <is>
           <t>有休シートの金額を使用</t>
         </is>
@@ -2564,330 +2641,370 @@
     <row r="20">
       <c r="A20" s="16" t="n"/>
       <c r="B20" s="18" t="n"/>
-      <c r="C20" s="20">
-        <f>IF(OR($A20="",C$6=""),"",IF(D$6="",$B20,ROUND($B20*C$7,0)))</f>
-        <v/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D20" s="20">
-        <f>IF(OR($A20="",D$6=""),"",IF(E$6="",$B20-SUM($C20:C20),ROUND($B20*D$7,0)))</f>
+        <f>IF(OR($A20="",D$6=""),"",IF(E$6="",$B20,IF($C20="最終週",0,IF($C20="均等",ROUND($B20/$D$4,0),ROUND($B20*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E20" s="20">
-        <f>IF(OR($A20="",E$6=""),"",IF(F$6="",$B20-SUM($C20:D20),ROUND($B20*E$7,0)))</f>
+        <f>IF(OR($A20="",E$6=""),"",IF(F$6="",$B20-SUM($D20:D20),IF($C20="最終週",0,IF($C20="均等",ROUND($B20/$D$4,0),ROUND($B20*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F20" s="20">
-        <f>IF(OR($A20="",F$6=""),"",IF(G$6="",$B20-SUM($C20:E20),ROUND($B20*F$7,0)))</f>
+        <f>IF(OR($A20="",F$6=""),"",IF(G$6="",$B20-SUM($D20:E20),IF($C20="最終週",0,IF($C20="均等",ROUND($B20/$D$4,0),ROUND($B20*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G20" s="20">
-        <f>IF(OR($A20="",G$6=""),"",IF(H$6="",$B20-SUM($C20:F20),ROUND($B20*G$7,0)))</f>
+        <f>IF(OR($A20="",G$6=""),"",IF(H$6="",$B20-SUM($D20:F20),IF($C20="最終週",0,IF($C20="均等",ROUND($B20/$D$4,0),ROUND($B20*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>IF(OR($A20="",H$6=""),"",$B20-SUM($C20:G20))</f>
-        <v/>
-      </c>
-      <c r="I20" s="21">
-        <f>IF($A20="","",SUM($C20:$H20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="20">
+        <f>IF(OR($A20="",H$6=""),"",IF(I$6="",$B20-SUM($D20:G20),IF($C20="最終週",0,IF($C20="均等",ROUND($B20/$D$4,0),ROUND($B20*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I20" s="20">
+        <f>IF(OR($A20="",I$6=""),"",$B20-SUM($D20:H20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="21">
+        <f>IF($A20="","",SUM(D20:I20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="20">
         <f>IF($A20="","",SUMIF(明細!$A$5:$A$104,$A20,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K20" s="20">
-        <f>IF(OR($A20="",$J20=0),"",$B20-$J20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="20">
+        <f>IF(OR($A20="",K20=0),"",$B20-K20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="32" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="n"/>
       <c r="B21" s="18" t="n"/>
-      <c r="C21" s="20">
-        <f>IF(OR($A21="",C$6=""),"",IF(D$6="",$B21,ROUND($B21*C$7,0)))</f>
-        <v/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D21" s="20">
-        <f>IF(OR($A21="",D$6=""),"",IF(E$6="",$B21-SUM($C21:C21),ROUND($B21*D$7,0)))</f>
+        <f>IF(OR($A21="",D$6=""),"",IF(E$6="",$B21,IF($C21="最終週",0,IF($C21="均等",ROUND($B21/$D$4,0),ROUND($B21*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f>IF(OR($A21="",E$6=""),"",IF(F$6="",$B21-SUM($C21:D21),ROUND($B21*E$7,0)))</f>
+        <f>IF(OR($A21="",E$6=""),"",IF(F$6="",$B21-SUM($D21:D21),IF($C21="最終週",0,IF($C21="均等",ROUND($B21/$D$4,0),ROUND($B21*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F21" s="20">
-        <f>IF(OR($A21="",F$6=""),"",IF(G$6="",$B21-SUM($C21:E21),ROUND($B21*F$7,0)))</f>
+        <f>IF(OR($A21="",F$6=""),"",IF(G$6="",$B21-SUM($D21:E21),IF($C21="最終週",0,IF($C21="均等",ROUND($B21/$D$4,0),ROUND($B21*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G21" s="20">
-        <f>IF(OR($A21="",G$6=""),"",IF(H$6="",$B21-SUM($C21:F21),ROUND($B21*G$7,0)))</f>
+        <f>IF(OR($A21="",G$6=""),"",IF(H$6="",$B21-SUM($D21:F21),IF($C21="最終週",0,IF($C21="均等",ROUND($B21/$D$4,0),ROUND($B21*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H21" s="20">
-        <f>IF(OR($A21="",H$6=""),"",$B21-SUM($C21:G21))</f>
-        <v/>
-      </c>
-      <c r="I21" s="21">
-        <f>IF($A21="","",SUM($C21:$H21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="20">
+        <f>IF(OR($A21="",H$6=""),"",IF(I$6="",$B21-SUM($D21:G21),IF($C21="最終週",0,IF($C21="均等",ROUND($B21/$D$4,0),ROUND($B21*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I21" s="20">
+        <f>IF(OR($A21="",I$6=""),"",$B21-SUM($D21:H21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="21">
+        <f>IF($A21="","",SUM(D21:I21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="20">
         <f>IF($A21="","",SUMIF(明細!$A$5:$A$104,$A21,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K21" s="20">
-        <f>IF(OR($A21="",$J21=0),"",$B21-$J21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="20">
+        <f>IF(OR($A21="",K21=0),"",$B21-K21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="32" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="n"/>
       <c r="B22" s="18" t="n"/>
-      <c r="C22" s="20">
-        <f>IF(OR($A22="",C$6=""),"",IF(D$6="",$B22,ROUND($B22*C$7,0)))</f>
-        <v/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D22" s="20">
-        <f>IF(OR($A22="",D$6=""),"",IF(E$6="",$B22-SUM($C22:C22),ROUND($B22*D$7,0)))</f>
+        <f>IF(OR($A22="",D$6=""),"",IF(E$6="",$B22,IF($C22="最終週",0,IF($C22="均等",ROUND($B22/$D$4,0),ROUND($B22*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E22" s="20">
-        <f>IF(OR($A22="",E$6=""),"",IF(F$6="",$B22-SUM($C22:D22),ROUND($B22*E$7,0)))</f>
+        <f>IF(OR($A22="",E$6=""),"",IF(F$6="",$B22-SUM($D22:D22),IF($C22="最終週",0,IF($C22="均等",ROUND($B22/$D$4,0),ROUND($B22*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F22" s="20">
-        <f>IF(OR($A22="",F$6=""),"",IF(G$6="",$B22-SUM($C22:E22),ROUND($B22*F$7,0)))</f>
+        <f>IF(OR($A22="",F$6=""),"",IF(G$6="",$B22-SUM($D22:E22),IF($C22="最終週",0,IF($C22="均等",ROUND($B22/$D$4,0),ROUND($B22*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G22" s="20">
-        <f>IF(OR($A22="",G$6=""),"",IF(H$6="",$B22-SUM($C22:F22),ROUND($B22*G$7,0)))</f>
+        <f>IF(OR($A22="",G$6=""),"",IF(H$6="",$B22-SUM($D22:F22),IF($C22="最終週",0,IF($C22="均等",ROUND($B22/$D$4,0),ROUND($B22*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H22" s="20">
-        <f>IF(OR($A22="",H$6=""),"",$B22-SUM($C22:G22))</f>
-        <v/>
-      </c>
-      <c r="I22" s="21">
-        <f>IF($A22="","",SUM($C22:$H22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="20">
+        <f>IF(OR($A22="",H$6=""),"",IF(I$6="",$B22-SUM($D22:G22),IF($C22="最終週",0,IF($C22="均等",ROUND($B22/$D$4,0),ROUND($B22*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I22" s="20">
+        <f>IF(OR($A22="",I$6=""),"",$B22-SUM($D22:H22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="21">
+        <f>IF($A22="","",SUM(D22:I22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="20">
         <f>IF($A22="","",SUMIF(明細!$A$5:$A$104,$A22,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K22" s="20">
-        <f>IF(OR($A22="",$J22=0),"",$B22-$J22)</f>
-        <v/>
-      </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="20">
+        <f>IF(OR($A22="",K22=0),"",$B22-K22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="32" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="n"/>
       <c r="B23" s="18" t="n"/>
-      <c r="C23" s="20">
-        <f>IF(OR($A23="",C$6=""),"",IF(D$6="",$B23,ROUND($B23*C$7,0)))</f>
-        <v/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D23" s="20">
-        <f>IF(OR($A23="",D$6=""),"",IF(E$6="",$B23-SUM($C23:C23),ROUND($B23*D$7,0)))</f>
+        <f>IF(OR($A23="",D$6=""),"",IF(E$6="",$B23,IF($C23="最終週",0,IF($C23="均等",ROUND($B23/$D$4,0),ROUND($B23*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f>IF(OR($A23="",E$6=""),"",IF(F$6="",$B23-SUM($C23:D23),ROUND($B23*E$7,0)))</f>
+        <f>IF(OR($A23="",E$6=""),"",IF(F$6="",$B23-SUM($D23:D23),IF($C23="最終週",0,IF($C23="均等",ROUND($B23/$D$4,0),ROUND($B23*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F23" s="20">
-        <f>IF(OR($A23="",F$6=""),"",IF(G$6="",$B23-SUM($C23:E23),ROUND($B23*F$7,0)))</f>
+        <f>IF(OR($A23="",F$6=""),"",IF(G$6="",$B23-SUM($D23:E23),IF($C23="最終週",0,IF($C23="均等",ROUND($B23/$D$4,0),ROUND($B23*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G23" s="20">
-        <f>IF(OR($A23="",G$6=""),"",IF(H$6="",$B23-SUM($C23:F23),ROUND($B23*G$7,0)))</f>
+        <f>IF(OR($A23="",G$6=""),"",IF(H$6="",$B23-SUM($D23:F23),IF($C23="最終週",0,IF($C23="均等",ROUND($B23/$D$4,0),ROUND($B23*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H23" s="20">
-        <f>IF(OR($A23="",H$6=""),"",$B23-SUM($C23:G23))</f>
-        <v/>
-      </c>
-      <c r="I23" s="21">
-        <f>IF($A23="","",SUM($C23:$H23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="20">
+        <f>IF(OR($A23="",H$6=""),"",IF(I$6="",$B23-SUM($D23:G23),IF($C23="最終週",0,IF($C23="均等",ROUND($B23/$D$4,0),ROUND($B23*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I23" s="20">
+        <f>IF(OR($A23="",I$6=""),"",$B23-SUM($D23:H23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="21">
+        <f>IF($A23="","",SUM(D23:I23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="20">
         <f>IF($A23="","",SUMIF(明細!$A$5:$A$104,$A23,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K23" s="20">
-        <f>IF(OR($A23="",$J23=0),"",$B23-$J23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="20">
+        <f>IF(OR($A23="",K23=0),"",$B23-K23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="32" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n"/>
       <c r="B24" s="18" t="n"/>
-      <c r="C24" s="20">
-        <f>IF(OR($A24="",C$6=""),"",IF(D$6="",$B24,ROUND($B24*C$7,0)))</f>
-        <v/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D24" s="20">
-        <f>IF(OR($A24="",D$6=""),"",IF(E$6="",$B24-SUM($C24:C24),ROUND($B24*D$7,0)))</f>
+        <f>IF(OR($A24="",D$6=""),"",IF(E$6="",$B24,IF($C24="最終週",0,IF($C24="均等",ROUND($B24/$D$4,0),ROUND($B24*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E24" s="20">
-        <f>IF(OR($A24="",E$6=""),"",IF(F$6="",$B24-SUM($C24:D24),ROUND($B24*E$7,0)))</f>
+        <f>IF(OR($A24="",E$6=""),"",IF(F$6="",$B24-SUM($D24:D24),IF($C24="最終週",0,IF($C24="均等",ROUND($B24/$D$4,0),ROUND($B24*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F24" s="20">
-        <f>IF(OR($A24="",F$6=""),"",IF(G$6="",$B24-SUM($C24:E24),ROUND($B24*F$7,0)))</f>
+        <f>IF(OR($A24="",F$6=""),"",IF(G$6="",$B24-SUM($D24:E24),IF($C24="最終週",0,IF($C24="均等",ROUND($B24/$D$4,0),ROUND($B24*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G24" s="20">
-        <f>IF(OR($A24="",G$6=""),"",IF(H$6="",$B24-SUM($C24:F24),ROUND($B24*G$7,0)))</f>
+        <f>IF(OR($A24="",G$6=""),"",IF(H$6="",$B24-SUM($D24:F24),IF($C24="最終週",0,IF($C24="均等",ROUND($B24/$D$4,0),ROUND($B24*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H24" s="20">
-        <f>IF(OR($A24="",H$6=""),"",$B24-SUM($C24:G24))</f>
-        <v/>
-      </c>
-      <c r="I24" s="21">
-        <f>IF($A24="","",SUM($C24:$H24))</f>
-        <v/>
-      </c>
-      <c r="J24" s="20">
+        <f>IF(OR($A24="",H$6=""),"",IF(I$6="",$B24-SUM($D24:G24),IF($C24="最終週",0,IF($C24="均等",ROUND($B24/$D$4,0),ROUND($B24*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I24" s="20">
+        <f>IF(OR($A24="",I$6=""),"",$B24-SUM($D24:H24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="21">
+        <f>IF($A24="","",SUM(D24:I24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="20">
         <f>IF($A24="","",SUMIF(明細!$A$5:$A$104,$A24,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K24" s="20">
-        <f>IF(OR($A24="",$J24=0),"",$B24-$J24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="20">
+        <f>IF(OR($A24="",K24=0),"",$B24-K24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="32" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="n"/>
       <c r="B25" s="18" t="n"/>
-      <c r="C25" s="20">
-        <f>IF(OR($A25="",C$6=""),"",IF(D$6="",$B25,ROUND($B25*C$7,0)))</f>
-        <v/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D25" s="20">
-        <f>IF(OR($A25="",D$6=""),"",IF(E$6="",$B25-SUM($C25:C25),ROUND($B25*D$7,0)))</f>
+        <f>IF(OR($A25="",D$6=""),"",IF(E$6="",$B25,IF($C25="最終週",0,IF($C25="均等",ROUND($B25/$D$4,0),ROUND($B25*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f>IF(OR($A25="",E$6=""),"",IF(F$6="",$B25-SUM($C25:D25),ROUND($B25*E$7,0)))</f>
+        <f>IF(OR($A25="",E$6=""),"",IF(F$6="",$B25-SUM($D25:D25),IF($C25="最終週",0,IF($C25="均等",ROUND($B25/$D$4,0),ROUND($B25*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F25" s="20">
-        <f>IF(OR($A25="",F$6=""),"",IF(G$6="",$B25-SUM($C25:E25),ROUND($B25*F$7,0)))</f>
+        <f>IF(OR($A25="",F$6=""),"",IF(G$6="",$B25-SUM($D25:E25),IF($C25="最終週",0,IF($C25="均等",ROUND($B25/$D$4,0),ROUND($B25*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G25" s="20">
-        <f>IF(OR($A25="",G$6=""),"",IF(H$6="",$B25-SUM($C25:F25),ROUND($B25*G$7,0)))</f>
+        <f>IF(OR($A25="",G$6=""),"",IF(H$6="",$B25-SUM($D25:F25),IF($C25="最終週",0,IF($C25="均等",ROUND($B25/$D$4,0),ROUND($B25*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H25" s="20">
-        <f>IF(OR($A25="",H$6=""),"",$B25-SUM($C25:G25))</f>
-        <v/>
-      </c>
-      <c r="I25" s="21">
-        <f>IF($A25="","",SUM($C25:$H25))</f>
-        <v/>
-      </c>
-      <c r="J25" s="20">
+        <f>IF(OR($A25="",H$6=""),"",IF(I$6="",$B25-SUM($D25:G25),IF($C25="最終週",0,IF($C25="均等",ROUND($B25/$D$4,0),ROUND($B25*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I25" s="20">
+        <f>IF(OR($A25="",I$6=""),"",$B25-SUM($D25:H25))</f>
+        <v/>
+      </c>
+      <c r="J25" s="21">
+        <f>IF($A25="","",SUM(D25:I25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="20">
         <f>IF($A25="","",SUMIF(明細!$A$5:$A$104,$A25,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K25" s="20">
-        <f>IF(OR($A25="",$J25=0),"",$B25-$J25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="16" t="n"/>
+      <c r="L25" s="20">
+        <f>IF(OR($A25="",K25=0),"",$B25-K25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="32" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n"/>
       <c r="B26" s="18" t="n"/>
-      <c r="C26" s="20">
-        <f>IF(OR($A26="",C$6=""),"",IF(D$6="",$B26,ROUND($B26*C$7,0)))</f>
-        <v/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D26" s="20">
-        <f>IF(OR($A26="",D$6=""),"",IF(E$6="",$B26-SUM($C26:C26),ROUND($B26*D$7,0)))</f>
+        <f>IF(OR($A26="",D$6=""),"",IF(E$6="",$B26,IF($C26="最終週",0,IF($C26="均等",ROUND($B26/$D$4,0),ROUND($B26*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E26" s="20">
-        <f>IF(OR($A26="",E$6=""),"",IF(F$6="",$B26-SUM($C26:D26),ROUND($B26*E$7,0)))</f>
+        <f>IF(OR($A26="",E$6=""),"",IF(F$6="",$B26-SUM($D26:D26),IF($C26="最終週",0,IF($C26="均等",ROUND($B26/$D$4,0),ROUND($B26*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F26" s="20">
-        <f>IF(OR($A26="",F$6=""),"",IF(G$6="",$B26-SUM($C26:E26),ROUND($B26*F$7,0)))</f>
+        <f>IF(OR($A26="",F$6=""),"",IF(G$6="",$B26-SUM($D26:E26),IF($C26="最終週",0,IF($C26="均等",ROUND($B26/$D$4,0),ROUND($B26*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G26" s="20">
-        <f>IF(OR($A26="",G$6=""),"",IF(H$6="",$B26-SUM($C26:F26),ROUND($B26*G$7,0)))</f>
+        <f>IF(OR($A26="",G$6=""),"",IF(H$6="",$B26-SUM($D26:F26),IF($C26="最終週",0,IF($C26="均等",ROUND($B26/$D$4,0),ROUND($B26*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H26" s="20">
-        <f>IF(OR($A26="",H$6=""),"",$B26-SUM($C26:G26))</f>
-        <v/>
-      </c>
-      <c r="I26" s="21">
-        <f>IF($A26="","",SUM($C26:$H26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="20">
+        <f>IF(OR($A26="",H$6=""),"",IF(I$6="",$B26-SUM($D26:G26),IF($C26="最終週",0,IF($C26="均等",ROUND($B26/$D$4,0),ROUND($B26*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I26" s="20">
+        <f>IF(OR($A26="",I$6=""),"",$B26-SUM($D26:H26))</f>
+        <v/>
+      </c>
+      <c r="J26" s="21">
+        <f>IF($A26="","",SUM(D26:I26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="20">
         <f>IF($A26="","",SUMIF(明細!$A$5:$A$104,$A26,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K26" s="20">
-        <f>IF(OR($A26="",$J26=0),"",$B26-$J26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="16" t="n"/>
+      <c r="L26" s="20">
+        <f>IF(OR($A26="",K26=0),"",$B26-K26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="32" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n"/>
       <c r="B27" s="18" t="n"/>
-      <c r="C27" s="20">
-        <f>IF(OR($A27="",C$6=""),"",IF(D$6="",$B27,ROUND($B27*C$7,0)))</f>
-        <v/>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
       </c>
       <c r="D27" s="20">
-        <f>IF(OR($A27="",D$6=""),"",IF(E$6="",$B27-SUM($C27:C27),ROUND($B27*D$7,0)))</f>
+        <f>IF(OR($A27="",D$6=""),"",IF(E$6="",$B27,IF($C27="最終週",0,IF($C27="均等",ROUND($B27/$D$4,0),ROUND($B27*D$7,0)))))</f>
         <v/>
       </c>
       <c r="E27" s="20">
-        <f>IF(OR($A27="",E$6=""),"",IF(F$6="",$B27-SUM($C27:D27),ROUND($B27*E$7,0)))</f>
+        <f>IF(OR($A27="",E$6=""),"",IF(F$6="",$B27-SUM($D27:D27),IF($C27="最終週",0,IF($C27="均等",ROUND($B27/$D$4,0),ROUND($B27*E$7,0)))))</f>
         <v/>
       </c>
       <c r="F27" s="20">
-        <f>IF(OR($A27="",F$6=""),"",IF(G$6="",$B27-SUM($C27:E27),ROUND($B27*F$7,0)))</f>
+        <f>IF(OR($A27="",F$6=""),"",IF(G$6="",$B27-SUM($D27:E27),IF($C27="最終週",0,IF($C27="均等",ROUND($B27/$D$4,0),ROUND($B27*F$7,0)))))</f>
         <v/>
       </c>
       <c r="G27" s="20">
-        <f>IF(OR($A27="",G$6=""),"",IF(H$6="",$B27-SUM($C27:F27),ROUND($B27*G$7,0)))</f>
+        <f>IF(OR($A27="",G$6=""),"",IF(H$6="",$B27-SUM($D27:F27),IF($C27="最終週",0,IF($C27="均等",ROUND($B27/$D$4,0),ROUND($B27*G$7,0)))))</f>
         <v/>
       </c>
       <c r="H27" s="20">
-        <f>IF(OR($A27="",H$6=""),"",$B27-SUM($C27:G27))</f>
-        <v/>
-      </c>
-      <c r="I27" s="21">
-        <f>IF($A27="","",SUM($C27:$H27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="20">
+        <f>IF(OR($A27="",H$6=""),"",IF(I$6="",$B27-SUM($D27:G27),IF($C27="最終週",0,IF($C27="均等",ROUND($B27/$D$4,0),ROUND($B27*H$7,0)))))</f>
+        <v/>
+      </c>
+      <c r="I27" s="20">
+        <f>IF(OR($A27="",I$6=""),"",$B27-SUM($D27:H27))</f>
+        <v/>
+      </c>
+      <c r="J27" s="21">
+        <f>IF($A27="","",SUM(D27:I27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="20">
         <f>IF($A27="","",SUMIF(明細!$A$5:$A$104,$A27,明細!$M$5:$M$104))</f>
         <v/>
       </c>
-      <c r="K27" s="20">
-        <f>IF(OR($A27="",$J27=0),"",$B27-$J27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="16" t="n"/>
+      <c r="L27" s="20">
+        <f>IF(OR($A27="",K27=0),"",$B27-K27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="32" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="26" t="inlineStr">
@@ -2899,10 +3016,7 @@
         <f>SUM($B$8:$B$27)</f>
         <v/>
       </c>
-      <c r="C29" s="24">
-        <f>IF(C$6="","",SUM(C$8:C$27))</f>
-        <v/>
-      </c>
+      <c r="C29" s="27" t="n"/>
       <c r="D29" s="24">
         <f>IF(D$6="","",SUM(D$8:D$27))</f>
         <v/>
@@ -2924,7 +3038,7 @@
         <v/>
       </c>
       <c r="I29" s="24">
-        <f>SUM($I$8:$I$27)</f>
+        <f>IF(I$6="","",SUM(I$8:I$27))</f>
         <v/>
       </c>
       <c r="J29" s="24">
@@ -2932,10 +3046,14 @@
         <v/>
       </c>
       <c r="K29" s="24">
-        <f>$B29-$J29</f>
-        <v/>
-      </c>
-      <c r="L29" s="27" t="n"/>
+        <f>SUM($K$8:$K$27)</f>
+        <v/>
+      </c>
+      <c r="L29" s="24">
+        <f>$B29-$K29</f>
+        <v/>
+      </c>
+      <c r="M29" s="27" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2951,7 +3069,7 @@
         </is>
       </c>
       <c r="B32" s="20">
-        <f>$I29-$B29</f>
+        <f>$J29-$B29</f>
         <v/>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2978,7 +3096,7 @@
         </is>
       </c>
       <c r="B34" s="20">
-        <f>$J29</f>
+        <f>$K29</f>
         <v/>
       </c>
     </row>
@@ -2999,13 +3117,61 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>※ 月予算だけ入れれば、動員予測の構成比どおりに週へ配分されます。「明細合計」は明細シートで積み上げた金額（参考）です。</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>■ 割振方法（C列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>動員比率</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>その週の動員構成比に応じて配分（既定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>最終週</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>その月の一番最後の週にまとめて計上（リーダー手当など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>均等</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>週数で等分（端数は最終週で調整）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>※ どの方法でも端数は最終週で調整するので、配分計は必ず月予算と一致します。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C8:C18 C20:C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="割振方法" error="「動員比率」「最終週」「均等」から選んでください" type="list">
+      <formula1>"動員比率,最終週,均等"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -3061,7 +3227,7 @@
           <t>週ごとの回数（日数）を入力</t>
         </is>
       </c>
-      <c r="N3" s="33" t="inlineStr">
+      <c r="N3" s="34" t="inlineStr">
         <is>
           <t>週別金額（自動計算）</t>
         </is>
@@ -3127,27 +3293,27 @@
           <t>金額計</t>
         </is>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="34">
         <f>設定!$B$21</f>
         <v/>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="34">
         <f>設定!$B$22</f>
         <v/>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="34">
         <f>設定!$B$23</f>
         <v/>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="34">
         <f>設定!$B$24</f>
         <v/>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="34">
         <f>設定!$B$25</f>
         <v/>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="34">
         <f>設定!$B$26</f>
         <v/>
       </c>
@@ -3166,29 +3332,29 @@
       <c r="C5" s="18" t="n">
         <v>1236</v>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="34" t="n">
+      <c r="E5" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="35" t="n">
+      <c r="G5" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="H5" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="35" t="n">
+      <c r="I5" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="35" t="n">
+      <c r="J5" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="35" t="n"/>
-      <c r="L5" s="36">
+      <c r="K5" s="36" t="n"/>
+      <c r="L5" s="37">
         <f>IF($A5="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F5:$K5))</f>
         <v/>
       </c>
@@ -3235,19 +3401,19 @@
       <c r="C6" s="18" t="n">
         <v>1226</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="35" t="n">
         <v>5.5</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="35" t="n"/>
-      <c r="I6" s="35" t="n"/>
-      <c r="J6" s="35" t="n"/>
-      <c r="K6" s="35" t="n"/>
-      <c r="L6" s="36">
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
+      <c r="J6" s="36" t="n"/>
+      <c r="K6" s="36" t="n"/>
+      <c r="L6" s="37">
         <f>IF($A6="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F6:$K6))</f>
         <v/>
       </c>
@@ -3294,19 +3460,19 @@
       <c r="C7" s="18" t="n">
         <v>1226</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="35" t="n">
         <v>2.15</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="35" t="n"/>
-      <c r="J7" s="35" t="n"/>
-      <c r="K7" s="35" t="n"/>
-      <c r="L7" s="36">
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="36" t="n"/>
+      <c r="K7" s="36" t="n"/>
+      <c r="L7" s="37">
         <f>IF($A7="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F7:$K7))</f>
         <v/>
       </c>
@@ -3353,19 +3519,19 @@
       <c r="C8" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D8" s="34" t="n">
+      <c r="D8" s="35" t="n">
         <v>5.5</v>
       </c>
-      <c r="E8" s="34" t="n">
+      <c r="E8" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="35" t="n"/>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="35" t="n"/>
-      <c r="J8" s="35" t="n"/>
-      <c r="K8" s="35" t="n"/>
-      <c r="L8" s="36">
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
+      <c r="L8" s="37">
         <f>IF($A8="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F8:$K8))</f>
         <v/>
       </c>
@@ -3412,19 +3578,19 @@
       <c r="C9" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D9" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="34" t="n">
+      <c r="E9" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="35" t="n"/>
-      <c r="J9" s="35" t="n"/>
-      <c r="K9" s="35" t="n"/>
-      <c r="L9" s="36">
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="36" t="n"/>
+      <c r="K9" s="36" t="n"/>
+      <c r="L9" s="37">
         <f>IF($A9="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F9:$K9))</f>
         <v/>
       </c>
@@ -3471,21 +3637,21 @@
       <c r="C10" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D10" s="34" t="n">
+      <c r="D10" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="34" t="n">
+      <c r="E10" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
-      <c r="J10" s="35" t="n"/>
-      <c r="K10" s="35" t="n"/>
-      <c r="L10" s="36">
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
+      <c r="L10" s="37">
         <f>IF($A10="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F10:$K10))</f>
         <v/>
       </c>
@@ -3532,21 +3698,21 @@
       <c r="C11" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D11" s="34" t="n">
+      <c r="D11" s="35" t="n">
         <v>1.5</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E11" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n">
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
-      <c r="J11" s="35" t="n"/>
-      <c r="K11" s="35" t="n"/>
-      <c r="L11" s="36">
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
+      <c r="K11" s="36" t="n"/>
+      <c r="L11" s="37">
         <f>IF($A11="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F11:$K11))</f>
         <v/>
       </c>
@@ -3593,21 +3759,21 @@
       <c r="C12" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="35" t="n">
         <v>1.75</v>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E12" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n">
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="35" t="n"/>
-      <c r="J12" s="35" t="n"/>
-      <c r="K12" s="35" t="n"/>
-      <c r="L12" s="36">
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
+      <c r="L12" s="37">
         <f>IF($A12="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F12:$K12))</f>
         <v/>
       </c>
@@ -3654,21 +3820,21 @@
       <c r="C13" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D13" s="34" t="n">
+      <c r="D13" s="35" t="n">
         <v>1.5</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E13" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n">
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="35" t="n"/>
-      <c r="K13" s="35" t="n"/>
-      <c r="L13" s="36">
+      <c r="J13" s="36" t="n"/>
+      <c r="K13" s="36" t="n"/>
+      <c r="L13" s="37">
         <f>IF($A13="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F13:$K13))</f>
         <v/>
       </c>
@@ -3715,21 +3881,21 @@
       <c r="C14" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D14" s="34" t="n">
+      <c r="D14" s="35" t="n">
         <v>0.5</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n"/>
-      <c r="K14" s="35" t="n"/>
-      <c r="L14" s="36">
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
+      <c r="L14" s="37">
         <f>IF($A14="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F14:$K14))</f>
         <v/>
       </c>
@@ -3776,21 +3942,21 @@
       <c r="C15" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="35" t="n">
         <v>0.5</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E15" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n">
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="35" t="n"/>
-      <c r="J15" s="35" t="n"/>
-      <c r="K15" s="35" t="n"/>
-      <c r="L15" s="36">
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="36" t="n"/>
+      <c r="L15" s="37">
         <f>IF($A15="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F15:$K15))</f>
         <v/>
       </c>
@@ -3837,21 +4003,21 @@
       <c r="C16" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D16" s="35" t="n">
         <v>0.75</v>
       </c>
-      <c r="E16" s="34" t="n">
+      <c r="E16" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n">
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="35" t="n"/>
-      <c r="J16" s="35" t="n"/>
-      <c r="K16" s="35" t="n"/>
-      <c r="L16" s="36">
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
+      <c r="L16" s="37">
         <f>IF($A16="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F16:$K16))</f>
         <v/>
       </c>
@@ -3898,21 +4064,21 @@
       <c r="C17" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D17" s="35" t="n">
         <v>0.75</v>
       </c>
-      <c r="E17" s="34" t="n">
+      <c r="E17" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
-      <c r="I17" s="35" t="n">
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="35" t="n"/>
-      <c r="K17" s="35" t="n"/>
-      <c r="L17" s="36">
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
+      <c r="L17" s="37">
         <f>IF($A17="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F17:$K17))</f>
         <v/>
       </c>
@@ -3959,19 +4125,19 @@
       <c r="C18" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D18" s="34" t="n">
+      <c r="D18" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="34" t="n">
+      <c r="E18" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
-      <c r="I18" s="35" t="n"/>
-      <c r="J18" s="35" t="n"/>
-      <c r="K18" s="35" t="n"/>
-      <c r="L18" s="36">
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
+      <c r="L18" s="37">
         <f>IF($A18="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F18:$K18))</f>
         <v/>
       </c>
@@ -4018,19 +4184,19 @@
       <c r="C19" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="34" t="n">
+      <c r="E19" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="35" t="n"/>
-      <c r="J19" s="35" t="n"/>
-      <c r="K19" s="35" t="n"/>
-      <c r="L19" s="36">
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
+      <c r="K19" s="36" t="n"/>
+      <c r="L19" s="37">
         <f>IF($A19="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F19:$K19))</f>
         <v/>
       </c>
@@ -4077,29 +4243,29 @@
       <c r="C20" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="34" t="n">
+      <c r="E20" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="35" t="n">
+      <c r="F20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="35" t="n">
+      <c r="G20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="35" t="n">
+      <c r="H20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="35" t="n">
+      <c r="I20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="35" t="n">
+      <c r="J20" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="35" t="n"/>
-      <c r="L20" s="36">
+      <c r="K20" s="36" t="n"/>
+      <c r="L20" s="37">
         <f>IF($A20="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F20:$K20))</f>
         <v/>
       </c>
@@ -4146,19 +4312,19 @@
       <c r="C21" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D21" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="35" t="n"/>
-      <c r="J21" s="35" t="n"/>
-      <c r="K21" s="35" t="n"/>
-      <c r="L21" s="36">
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="36" t="n"/>
+      <c r="L21" s="37">
         <f>IF($A21="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F21:$K21))</f>
         <v/>
       </c>
@@ -4205,19 +4371,19 @@
       <c r="C22" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D22" s="34" t="n">
+      <c r="D22" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="E22" s="34" t="n">
+      <c r="E22" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="35" t="n"/>
-      <c r="G22" s="35" t="n"/>
-      <c r="H22" s="35" t="n"/>
-      <c r="I22" s="35" t="n"/>
-      <c r="J22" s="35" t="n"/>
-      <c r="K22" s="35" t="n"/>
-      <c r="L22" s="36">
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="36" t="n"/>
+      <c r="L22" s="37">
         <f>IF($A22="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F22:$K22))</f>
         <v/>
       </c>
@@ -4264,19 +4430,19 @@
       <c r="C23" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D23" s="34" t="n">
+      <c r="D23" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="34" t="n">
+      <c r="E23" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="35" t="n"/>
-      <c r="J23" s="35" t="n"/>
-      <c r="K23" s="35" t="n"/>
-      <c r="L23" s="36">
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n"/>
+      <c r="J23" s="36" t="n"/>
+      <c r="K23" s="36" t="n"/>
+      <c r="L23" s="37">
         <f>IF($A23="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F23:$K23))</f>
         <v/>
       </c>
@@ -4319,15 +4485,15 @@
       <c r="C24" s="18" t="n">
         <v>1251</v>
       </c>
-      <c r="D24" s="34" t="n"/>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
-      <c r="J24" s="35" t="n"/>
-      <c r="K24" s="35" t="n"/>
-      <c r="L24" s="36">
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
+      <c r="L24" s="37">
         <f>IF($A24="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F24:$K24))</f>
         <v/>
       </c>
@@ -4374,19 +4540,19 @@
       <c r="C25" s="18" t="n">
         <v>93000</v>
       </c>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="34" t="n">
+      <c r="E25" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="35" t="n"/>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n"/>
-      <c r="I25" s="35" t="n"/>
-      <c r="J25" s="35" t="n"/>
-      <c r="K25" s="35" t="n"/>
-      <c r="L25" s="36">
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="36" t="n"/>
+      <c r="K25" s="36" t="n"/>
+      <c r="L25" s="37">
         <f>IF($A25="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F25:$K25))</f>
         <v/>
       </c>
@@ -4423,15 +4589,15 @@
       <c r="A26" s="16" t="n"/>
       <c r="B26" s="16" t="n"/>
       <c r="C26" s="18" t="n"/>
-      <c r="D26" s="34" t="n"/>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="35" t="n"/>
-      <c r="G26" s="35" t="n"/>
-      <c r="H26" s="35" t="n"/>
-      <c r="I26" s="35" t="n"/>
-      <c r="J26" s="35" t="n"/>
-      <c r="K26" s="35" t="n"/>
-      <c r="L26" s="36">
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
+      <c r="L26" s="37">
         <f>IF($A26="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F26:$K26))</f>
         <v/>
       </c>
@@ -4468,15 +4634,15 @@
       <c r="A27" s="16" t="n"/>
       <c r="B27" s="16" t="n"/>
       <c r="C27" s="18" t="n"/>
-      <c r="D27" s="34" t="n"/>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="35" t="n"/>
-      <c r="G27" s="35" t="n"/>
-      <c r="H27" s="35" t="n"/>
-      <c r="I27" s="35" t="n"/>
-      <c r="J27" s="35" t="n"/>
-      <c r="K27" s="35" t="n"/>
-      <c r="L27" s="36">
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="36" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="36" t="n"/>
+      <c r="I27" s="36" t="n"/>
+      <c r="J27" s="36" t="n"/>
+      <c r="K27" s="36" t="n"/>
+      <c r="L27" s="37">
         <f>IF($A27="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F27:$K27))</f>
         <v/>
       </c>
@@ -4513,15 +4679,15 @@
       <c r="A28" s="16" t="n"/>
       <c r="B28" s="16" t="n"/>
       <c r="C28" s="18" t="n"/>
-      <c r="D28" s="34" t="n"/>
-      <c r="E28" s="34" t="n"/>
-      <c r="F28" s="35" t="n"/>
-      <c r="G28" s="35" t="n"/>
-      <c r="H28" s="35" t="n"/>
-      <c r="I28" s="35" t="n"/>
-      <c r="J28" s="35" t="n"/>
-      <c r="K28" s="35" t="n"/>
-      <c r="L28" s="36">
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="36" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="36" t="n"/>
+      <c r="I28" s="36" t="n"/>
+      <c r="J28" s="36" t="n"/>
+      <c r="K28" s="36" t="n"/>
+      <c r="L28" s="37">
         <f>IF($A28="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F28:$K28))</f>
         <v/>
       </c>
@@ -4558,15 +4724,15 @@
       <c r="A29" s="16" t="n"/>
       <c r="B29" s="16" t="n"/>
       <c r="C29" s="18" t="n"/>
-      <c r="D29" s="34" t="n"/>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="35" t="n"/>
-      <c r="G29" s="35" t="n"/>
-      <c r="H29" s="35" t="n"/>
-      <c r="I29" s="35" t="n"/>
-      <c r="J29" s="35" t="n"/>
-      <c r="K29" s="35" t="n"/>
-      <c r="L29" s="36">
+      <c r="D29" s="35" t="n"/>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="36" t="n"/>
+      <c r="H29" s="36" t="n"/>
+      <c r="I29" s="36" t="n"/>
+      <c r="J29" s="36" t="n"/>
+      <c r="K29" s="36" t="n"/>
+      <c r="L29" s="37">
         <f>IF($A29="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F29:$K29))</f>
         <v/>
       </c>
@@ -4603,15 +4769,15 @@
       <c r="A30" s="16" t="n"/>
       <c r="B30" s="16" t="n"/>
       <c r="C30" s="18" t="n"/>
-      <c r="D30" s="34" t="n"/>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="35" t="n"/>
-      <c r="G30" s="35" t="n"/>
-      <c r="H30" s="35" t="n"/>
-      <c r="I30" s="35" t="n"/>
-      <c r="J30" s="35" t="n"/>
-      <c r="K30" s="35" t="n"/>
-      <c r="L30" s="36">
+      <c r="D30" s="35" t="n"/>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
+      <c r="J30" s="36" t="n"/>
+      <c r="K30" s="36" t="n"/>
+      <c r="L30" s="37">
         <f>IF($A30="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F30:$K30))</f>
         <v/>
       </c>
@@ -4648,15 +4814,15 @@
       <c r="A31" s="16" t="n"/>
       <c r="B31" s="16" t="n"/>
       <c r="C31" s="18" t="n"/>
-      <c r="D31" s="34" t="n"/>
-      <c r="E31" s="34" t="n"/>
-      <c r="F31" s="35" t="n"/>
-      <c r="G31" s="35" t="n"/>
-      <c r="H31" s="35" t="n"/>
-      <c r="I31" s="35" t="n"/>
-      <c r="J31" s="35" t="n"/>
-      <c r="K31" s="35" t="n"/>
-      <c r="L31" s="36">
+      <c r="D31" s="35" t="n"/>
+      <c r="E31" s="35" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="36" t="n"/>
+      <c r="I31" s="36" t="n"/>
+      <c r="J31" s="36" t="n"/>
+      <c r="K31" s="36" t="n"/>
+      <c r="L31" s="37">
         <f>IF($A31="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F31:$K31))</f>
         <v/>
       </c>
@@ -4693,15 +4859,15 @@
       <c r="A32" s="16" t="n"/>
       <c r="B32" s="16" t="n"/>
       <c r="C32" s="18" t="n"/>
-      <c r="D32" s="34" t="n"/>
-      <c r="E32" s="34" t="n"/>
-      <c r="F32" s="35" t="n"/>
-      <c r="G32" s="35" t="n"/>
-      <c r="H32" s="35" t="n"/>
-      <c r="I32" s="35" t="n"/>
-      <c r="J32" s="35" t="n"/>
-      <c r="K32" s="35" t="n"/>
-      <c r="L32" s="36">
+      <c r="D32" s="35" t="n"/>
+      <c r="E32" s="35" t="n"/>
+      <c r="F32" s="36" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="36" t="n"/>
+      <c r="I32" s="36" t="n"/>
+      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="36" t="n"/>
+      <c r="L32" s="37">
         <f>IF($A32="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F32:$K32))</f>
         <v/>
       </c>
@@ -4738,15 +4904,15 @@
       <c r="A33" s="16" t="n"/>
       <c r="B33" s="16" t="n"/>
       <c r="C33" s="18" t="n"/>
-      <c r="D33" s="34" t="n"/>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="35" t="n"/>
-      <c r="G33" s="35" t="n"/>
-      <c r="H33" s="35" t="n"/>
-      <c r="I33" s="35" t="n"/>
-      <c r="J33" s="35" t="n"/>
-      <c r="K33" s="35" t="n"/>
-      <c r="L33" s="36">
+      <c r="D33" s="35" t="n"/>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="36" t="n"/>
+      <c r="G33" s="36" t="n"/>
+      <c r="H33" s="36" t="n"/>
+      <c r="I33" s="36" t="n"/>
+      <c r="J33" s="36" t="n"/>
+      <c r="K33" s="36" t="n"/>
+      <c r="L33" s="37">
         <f>IF($A33="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F33:$K33))</f>
         <v/>
       </c>
@@ -4783,15 +4949,15 @@
       <c r="A34" s="16" t="n"/>
       <c r="B34" s="16" t="n"/>
       <c r="C34" s="18" t="n"/>
-      <c r="D34" s="34" t="n"/>
-      <c r="E34" s="34" t="n"/>
-      <c r="F34" s="35" t="n"/>
-      <c r="G34" s="35" t="n"/>
-      <c r="H34" s="35" t="n"/>
-      <c r="I34" s="35" t="n"/>
-      <c r="J34" s="35" t="n"/>
-      <c r="K34" s="35" t="n"/>
-      <c r="L34" s="36">
+      <c r="D34" s="35" t="n"/>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="36" t="n"/>
+      <c r="G34" s="36" t="n"/>
+      <c r="H34" s="36" t="n"/>
+      <c r="I34" s="36" t="n"/>
+      <c r="J34" s="36" t="n"/>
+      <c r="K34" s="36" t="n"/>
+      <c r="L34" s="37">
         <f>IF($A34="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F34:$K34))</f>
         <v/>
       </c>
@@ -4828,15 +4994,15 @@
       <c r="A35" s="16" t="n"/>
       <c r="B35" s="16" t="n"/>
       <c r="C35" s="18" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="35" t="n"/>
-      <c r="G35" s="35" t="n"/>
-      <c r="H35" s="35" t="n"/>
-      <c r="I35" s="35" t="n"/>
-      <c r="J35" s="35" t="n"/>
-      <c r="K35" s="35" t="n"/>
-      <c r="L35" s="36">
+      <c r="D35" s="35" t="n"/>
+      <c r="E35" s="35" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
+      <c r="J35" s="36" t="n"/>
+      <c r="K35" s="36" t="n"/>
+      <c r="L35" s="37">
         <f>IF($A35="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F35:$K35))</f>
         <v/>
       </c>
@@ -4873,15 +5039,15 @@
       <c r="A36" s="16" t="n"/>
       <c r="B36" s="16" t="n"/>
       <c r="C36" s="18" t="n"/>
-      <c r="D36" s="34" t="n"/>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="35" t="n"/>
-      <c r="G36" s="35" t="n"/>
-      <c r="H36" s="35" t="n"/>
-      <c r="I36" s="35" t="n"/>
-      <c r="J36" s="35" t="n"/>
-      <c r="K36" s="35" t="n"/>
-      <c r="L36" s="36">
+      <c r="D36" s="35" t="n"/>
+      <c r="E36" s="35" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
+      <c r="J36" s="36" t="n"/>
+      <c r="K36" s="36" t="n"/>
+      <c r="L36" s="37">
         <f>IF($A36="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F36:$K36))</f>
         <v/>
       </c>
@@ -4918,15 +5084,15 @@
       <c r="A37" s="16" t="n"/>
       <c r="B37" s="16" t="n"/>
       <c r="C37" s="18" t="n"/>
-      <c r="D37" s="34" t="n"/>
-      <c r="E37" s="34" t="n"/>
-      <c r="F37" s="35" t="n"/>
-      <c r="G37" s="35" t="n"/>
-      <c r="H37" s="35" t="n"/>
-      <c r="I37" s="35" t="n"/>
-      <c r="J37" s="35" t="n"/>
-      <c r="K37" s="35" t="n"/>
-      <c r="L37" s="36">
+      <c r="D37" s="35" t="n"/>
+      <c r="E37" s="35" t="n"/>
+      <c r="F37" s="36" t="n"/>
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="36" t="n"/>
+      <c r="I37" s="36" t="n"/>
+      <c r="J37" s="36" t="n"/>
+      <c r="K37" s="36" t="n"/>
+      <c r="L37" s="37">
         <f>IF($A37="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F37:$K37))</f>
         <v/>
       </c>
@@ -4963,15 +5129,15 @@
       <c r="A38" s="16" t="n"/>
       <c r="B38" s="16" t="n"/>
       <c r="C38" s="18" t="n"/>
-      <c r="D38" s="34" t="n"/>
-      <c r="E38" s="34" t="n"/>
-      <c r="F38" s="35" t="n"/>
-      <c r="G38" s="35" t="n"/>
-      <c r="H38" s="35" t="n"/>
-      <c r="I38" s="35" t="n"/>
-      <c r="J38" s="35" t="n"/>
-      <c r="K38" s="35" t="n"/>
-      <c r="L38" s="36">
+      <c r="D38" s="35" t="n"/>
+      <c r="E38" s="35" t="n"/>
+      <c r="F38" s="36" t="n"/>
+      <c r="G38" s="36" t="n"/>
+      <c r="H38" s="36" t="n"/>
+      <c r="I38" s="36" t="n"/>
+      <c r="J38" s="36" t="n"/>
+      <c r="K38" s="36" t="n"/>
+      <c r="L38" s="37">
         <f>IF($A38="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F38:$K38))</f>
         <v/>
       </c>
@@ -5008,15 +5174,15 @@
       <c r="A39" s="16" t="n"/>
       <c r="B39" s="16" t="n"/>
       <c r="C39" s="18" t="n"/>
-      <c r="D39" s="34" t="n"/>
-      <c r="E39" s="34" t="n"/>
-      <c r="F39" s="35" t="n"/>
-      <c r="G39" s="35" t="n"/>
-      <c r="H39" s="35" t="n"/>
-      <c r="I39" s="35" t="n"/>
-      <c r="J39" s="35" t="n"/>
-      <c r="K39" s="35" t="n"/>
-      <c r="L39" s="36">
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="36" t="n"/>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="36" t="n"/>
+      <c r="I39" s="36" t="n"/>
+      <c r="J39" s="36" t="n"/>
+      <c r="K39" s="36" t="n"/>
+      <c r="L39" s="37">
         <f>IF($A39="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F39:$K39))</f>
         <v/>
       </c>
@@ -5053,15 +5219,15 @@
       <c r="A40" s="16" t="n"/>
       <c r="B40" s="16" t="n"/>
       <c r="C40" s="18" t="n"/>
-      <c r="D40" s="34" t="n"/>
-      <c r="E40" s="34" t="n"/>
-      <c r="F40" s="35" t="n"/>
-      <c r="G40" s="35" t="n"/>
-      <c r="H40" s="35" t="n"/>
-      <c r="I40" s="35" t="n"/>
-      <c r="J40" s="35" t="n"/>
-      <c r="K40" s="35" t="n"/>
-      <c r="L40" s="36">
+      <c r="D40" s="35" t="n"/>
+      <c r="E40" s="35" t="n"/>
+      <c r="F40" s="36" t="n"/>
+      <c r="G40" s="36" t="n"/>
+      <c r="H40" s="36" t="n"/>
+      <c r="I40" s="36" t="n"/>
+      <c r="J40" s="36" t="n"/>
+      <c r="K40" s="36" t="n"/>
+      <c r="L40" s="37">
         <f>IF($A40="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F40:$K40))</f>
         <v/>
       </c>
@@ -5098,15 +5264,15 @@
       <c r="A41" s="16" t="n"/>
       <c r="B41" s="16" t="n"/>
       <c r="C41" s="18" t="n"/>
-      <c r="D41" s="34" t="n"/>
-      <c r="E41" s="34" t="n"/>
-      <c r="F41" s="35" t="n"/>
-      <c r="G41" s="35" t="n"/>
-      <c r="H41" s="35" t="n"/>
-      <c r="I41" s="35" t="n"/>
-      <c r="J41" s="35" t="n"/>
-      <c r="K41" s="35" t="n"/>
-      <c r="L41" s="36">
+      <c r="D41" s="35" t="n"/>
+      <c r="E41" s="35" t="n"/>
+      <c r="F41" s="36" t="n"/>
+      <c r="G41" s="36" t="n"/>
+      <c r="H41" s="36" t="n"/>
+      <c r="I41" s="36" t="n"/>
+      <c r="J41" s="36" t="n"/>
+      <c r="K41" s="36" t="n"/>
+      <c r="L41" s="37">
         <f>IF($A41="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F41:$K41))</f>
         <v/>
       </c>
@@ -5143,15 +5309,15 @@
       <c r="A42" s="16" t="n"/>
       <c r="B42" s="16" t="n"/>
       <c r="C42" s="18" t="n"/>
-      <c r="D42" s="34" t="n"/>
-      <c r="E42" s="34" t="n"/>
-      <c r="F42" s="35" t="n"/>
-      <c r="G42" s="35" t="n"/>
-      <c r="H42" s="35" t="n"/>
-      <c r="I42" s="35" t="n"/>
-      <c r="J42" s="35" t="n"/>
-      <c r="K42" s="35" t="n"/>
-      <c r="L42" s="36">
+      <c r="D42" s="35" t="n"/>
+      <c r="E42" s="35" t="n"/>
+      <c r="F42" s="36" t="n"/>
+      <c r="G42" s="36" t="n"/>
+      <c r="H42" s="36" t="n"/>
+      <c r="I42" s="36" t="n"/>
+      <c r="J42" s="36" t="n"/>
+      <c r="K42" s="36" t="n"/>
+      <c r="L42" s="37">
         <f>IF($A42="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F42:$K42))</f>
         <v/>
       </c>
@@ -5188,15 +5354,15 @@
       <c r="A43" s="16" t="n"/>
       <c r="B43" s="16" t="n"/>
       <c r="C43" s="18" t="n"/>
-      <c r="D43" s="34" t="n"/>
-      <c r="E43" s="34" t="n"/>
-      <c r="F43" s="35" t="n"/>
-      <c r="G43" s="35" t="n"/>
-      <c r="H43" s="35" t="n"/>
-      <c r="I43" s="35" t="n"/>
-      <c r="J43" s="35" t="n"/>
-      <c r="K43" s="35" t="n"/>
-      <c r="L43" s="36">
+      <c r="D43" s="35" t="n"/>
+      <c r="E43" s="35" t="n"/>
+      <c r="F43" s="36" t="n"/>
+      <c r="G43" s="36" t="n"/>
+      <c r="H43" s="36" t="n"/>
+      <c r="I43" s="36" t="n"/>
+      <c r="J43" s="36" t="n"/>
+      <c r="K43" s="36" t="n"/>
+      <c r="L43" s="37">
         <f>IF($A43="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F43:$K43))</f>
         <v/>
       </c>
@@ -5233,15 +5399,15 @@
       <c r="A44" s="16" t="n"/>
       <c r="B44" s="16" t="n"/>
       <c r="C44" s="18" t="n"/>
-      <c r="D44" s="34" t="n"/>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="35" t="n"/>
-      <c r="G44" s="35" t="n"/>
-      <c r="H44" s="35" t="n"/>
-      <c r="I44" s="35" t="n"/>
-      <c r="J44" s="35" t="n"/>
-      <c r="K44" s="35" t="n"/>
-      <c r="L44" s="36">
+      <c r="D44" s="35" t="n"/>
+      <c r="E44" s="35" t="n"/>
+      <c r="F44" s="36" t="n"/>
+      <c r="G44" s="36" t="n"/>
+      <c r="H44" s="36" t="n"/>
+      <c r="I44" s="36" t="n"/>
+      <c r="J44" s="36" t="n"/>
+      <c r="K44" s="36" t="n"/>
+      <c r="L44" s="37">
         <f>IF($A44="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F44:$K44))</f>
         <v/>
       </c>
@@ -5278,15 +5444,15 @@
       <c r="A45" s="16" t="n"/>
       <c r="B45" s="16" t="n"/>
       <c r="C45" s="18" t="n"/>
-      <c r="D45" s="34" t="n"/>
-      <c r="E45" s="34" t="n"/>
-      <c r="F45" s="35" t="n"/>
-      <c r="G45" s="35" t="n"/>
-      <c r="H45" s="35" t="n"/>
-      <c r="I45" s="35" t="n"/>
-      <c r="J45" s="35" t="n"/>
-      <c r="K45" s="35" t="n"/>
-      <c r="L45" s="36">
+      <c r="D45" s="35" t="n"/>
+      <c r="E45" s="35" t="n"/>
+      <c r="F45" s="36" t="n"/>
+      <c r="G45" s="36" t="n"/>
+      <c r="H45" s="36" t="n"/>
+      <c r="I45" s="36" t="n"/>
+      <c r="J45" s="36" t="n"/>
+      <c r="K45" s="36" t="n"/>
+      <c r="L45" s="37">
         <f>IF($A45="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F45:$K45))</f>
         <v/>
       </c>
@@ -5323,15 +5489,15 @@
       <c r="A46" s="16" t="n"/>
       <c r="B46" s="16" t="n"/>
       <c r="C46" s="18" t="n"/>
-      <c r="D46" s="34" t="n"/>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="35" t="n"/>
-      <c r="G46" s="35" t="n"/>
-      <c r="H46" s="35" t="n"/>
-      <c r="I46" s="35" t="n"/>
-      <c r="J46" s="35" t="n"/>
-      <c r="K46" s="35" t="n"/>
-      <c r="L46" s="36">
+      <c r="D46" s="35" t="n"/>
+      <c r="E46" s="35" t="n"/>
+      <c r="F46" s="36" t="n"/>
+      <c r="G46" s="36" t="n"/>
+      <c r="H46" s="36" t="n"/>
+      <c r="I46" s="36" t="n"/>
+      <c r="J46" s="36" t="n"/>
+      <c r="K46" s="36" t="n"/>
+      <c r="L46" s="37">
         <f>IF($A46="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F46:$K46))</f>
         <v/>
       </c>
@@ -5368,15 +5534,15 @@
       <c r="A47" s="16" t="n"/>
       <c r="B47" s="16" t="n"/>
       <c r="C47" s="18" t="n"/>
-      <c r="D47" s="34" t="n"/>
-      <c r="E47" s="34" t="n"/>
-      <c r="F47" s="35" t="n"/>
-      <c r="G47" s="35" t="n"/>
-      <c r="H47" s="35" t="n"/>
-      <c r="I47" s="35" t="n"/>
-      <c r="J47" s="35" t="n"/>
-      <c r="K47" s="35" t="n"/>
-      <c r="L47" s="36">
+      <c r="D47" s="35" t="n"/>
+      <c r="E47" s="35" t="n"/>
+      <c r="F47" s="36" t="n"/>
+      <c r="G47" s="36" t="n"/>
+      <c r="H47" s="36" t="n"/>
+      <c r="I47" s="36" t="n"/>
+      <c r="J47" s="36" t="n"/>
+      <c r="K47" s="36" t="n"/>
+      <c r="L47" s="37">
         <f>IF($A47="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F47:$K47))</f>
         <v/>
       </c>
@@ -5413,15 +5579,15 @@
       <c r="A48" s="16" t="n"/>
       <c r="B48" s="16" t="n"/>
       <c r="C48" s="18" t="n"/>
-      <c r="D48" s="34" t="n"/>
-      <c r="E48" s="34" t="n"/>
-      <c r="F48" s="35" t="n"/>
-      <c r="G48" s="35" t="n"/>
-      <c r="H48" s="35" t="n"/>
-      <c r="I48" s="35" t="n"/>
-      <c r="J48" s="35" t="n"/>
-      <c r="K48" s="35" t="n"/>
-      <c r="L48" s="36">
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="35" t="n"/>
+      <c r="F48" s="36" t="n"/>
+      <c r="G48" s="36" t="n"/>
+      <c r="H48" s="36" t="n"/>
+      <c r="I48" s="36" t="n"/>
+      <c r="J48" s="36" t="n"/>
+      <c r="K48" s="36" t="n"/>
+      <c r="L48" s="37">
         <f>IF($A48="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F48:$K48))</f>
         <v/>
       </c>
@@ -5458,15 +5624,15 @@
       <c r="A49" s="16" t="n"/>
       <c r="B49" s="16" t="n"/>
       <c r="C49" s="18" t="n"/>
-      <c r="D49" s="34" t="n"/>
-      <c r="E49" s="34" t="n"/>
-      <c r="F49" s="35" t="n"/>
-      <c r="G49" s="35" t="n"/>
-      <c r="H49" s="35" t="n"/>
-      <c r="I49" s="35" t="n"/>
-      <c r="J49" s="35" t="n"/>
-      <c r="K49" s="35" t="n"/>
-      <c r="L49" s="36">
+      <c r="D49" s="35" t="n"/>
+      <c r="E49" s="35" t="n"/>
+      <c r="F49" s="36" t="n"/>
+      <c r="G49" s="36" t="n"/>
+      <c r="H49" s="36" t="n"/>
+      <c r="I49" s="36" t="n"/>
+      <c r="J49" s="36" t="n"/>
+      <c r="K49" s="36" t="n"/>
+      <c r="L49" s="37">
         <f>IF($A49="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F49:$K49))</f>
         <v/>
       </c>
@@ -5503,15 +5669,15 @@
       <c r="A50" s="16" t="n"/>
       <c r="B50" s="16" t="n"/>
       <c r="C50" s="18" t="n"/>
-      <c r="D50" s="34" t="n"/>
-      <c r="E50" s="34" t="n"/>
-      <c r="F50" s="35" t="n"/>
-      <c r="G50" s="35" t="n"/>
-      <c r="H50" s="35" t="n"/>
-      <c r="I50" s="35" t="n"/>
-      <c r="J50" s="35" t="n"/>
-      <c r="K50" s="35" t="n"/>
-      <c r="L50" s="36">
+      <c r="D50" s="35" t="n"/>
+      <c r="E50" s="35" t="n"/>
+      <c r="F50" s="36" t="n"/>
+      <c r="G50" s="36" t="n"/>
+      <c r="H50" s="36" t="n"/>
+      <c r="I50" s="36" t="n"/>
+      <c r="J50" s="36" t="n"/>
+      <c r="K50" s="36" t="n"/>
+      <c r="L50" s="37">
         <f>IF($A50="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F50:$K50))</f>
         <v/>
       </c>
@@ -5548,15 +5714,15 @@
       <c r="A51" s="16" t="n"/>
       <c r="B51" s="16" t="n"/>
       <c r="C51" s="18" t="n"/>
-      <c r="D51" s="34" t="n"/>
-      <c r="E51" s="34" t="n"/>
-      <c r="F51" s="35" t="n"/>
-      <c r="G51" s="35" t="n"/>
-      <c r="H51" s="35" t="n"/>
-      <c r="I51" s="35" t="n"/>
-      <c r="J51" s="35" t="n"/>
-      <c r="K51" s="35" t="n"/>
-      <c r="L51" s="36">
+      <c r="D51" s="35" t="n"/>
+      <c r="E51" s="35" t="n"/>
+      <c r="F51" s="36" t="n"/>
+      <c r="G51" s="36" t="n"/>
+      <c r="H51" s="36" t="n"/>
+      <c r="I51" s="36" t="n"/>
+      <c r="J51" s="36" t="n"/>
+      <c r="K51" s="36" t="n"/>
+      <c r="L51" s="37">
         <f>IF($A51="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F51:$K51))</f>
         <v/>
       </c>
@@ -5593,15 +5759,15 @@
       <c r="A52" s="16" t="n"/>
       <c r="B52" s="16" t="n"/>
       <c r="C52" s="18" t="n"/>
-      <c r="D52" s="34" t="n"/>
-      <c r="E52" s="34" t="n"/>
-      <c r="F52" s="35" t="n"/>
-      <c r="G52" s="35" t="n"/>
-      <c r="H52" s="35" t="n"/>
-      <c r="I52" s="35" t="n"/>
-      <c r="J52" s="35" t="n"/>
-      <c r="K52" s="35" t="n"/>
-      <c r="L52" s="36">
+      <c r="D52" s="35" t="n"/>
+      <c r="E52" s="35" t="n"/>
+      <c r="F52" s="36" t="n"/>
+      <c r="G52" s="36" t="n"/>
+      <c r="H52" s="36" t="n"/>
+      <c r="I52" s="36" t="n"/>
+      <c r="J52" s="36" t="n"/>
+      <c r="K52" s="36" t="n"/>
+      <c r="L52" s="37">
         <f>IF($A52="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F52:$K52))</f>
         <v/>
       </c>
@@ -5638,15 +5804,15 @@
       <c r="A53" s="16" t="n"/>
       <c r="B53" s="16" t="n"/>
       <c r="C53" s="18" t="n"/>
-      <c r="D53" s="34" t="n"/>
-      <c r="E53" s="34" t="n"/>
-      <c r="F53" s="35" t="n"/>
-      <c r="G53" s="35" t="n"/>
-      <c r="H53" s="35" t="n"/>
-      <c r="I53" s="35" t="n"/>
-      <c r="J53" s="35" t="n"/>
-      <c r="K53" s="35" t="n"/>
-      <c r="L53" s="36">
+      <c r="D53" s="35" t="n"/>
+      <c r="E53" s="35" t="n"/>
+      <c r="F53" s="36" t="n"/>
+      <c r="G53" s="36" t="n"/>
+      <c r="H53" s="36" t="n"/>
+      <c r="I53" s="36" t="n"/>
+      <c r="J53" s="36" t="n"/>
+      <c r="K53" s="36" t="n"/>
+      <c r="L53" s="37">
         <f>IF($A53="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F53:$K53))</f>
         <v/>
       </c>
@@ -5683,15 +5849,15 @@
       <c r="A54" s="16" t="n"/>
       <c r="B54" s="16" t="n"/>
       <c r="C54" s="18" t="n"/>
-      <c r="D54" s="34" t="n"/>
-      <c r="E54" s="34" t="n"/>
-      <c r="F54" s="35" t="n"/>
-      <c r="G54" s="35" t="n"/>
-      <c r="H54" s="35" t="n"/>
-      <c r="I54" s="35" t="n"/>
-      <c r="J54" s="35" t="n"/>
-      <c r="K54" s="35" t="n"/>
-      <c r="L54" s="36">
+      <c r="D54" s="35" t="n"/>
+      <c r="E54" s="35" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="36" t="n"/>
+      <c r="H54" s="36" t="n"/>
+      <c r="I54" s="36" t="n"/>
+      <c r="J54" s="36" t="n"/>
+      <c r="K54" s="36" t="n"/>
+      <c r="L54" s="37">
         <f>IF($A54="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F54:$K54))</f>
         <v/>
       </c>
@@ -5728,15 +5894,15 @@
       <c r="A55" s="16" t="n"/>
       <c r="B55" s="16" t="n"/>
       <c r="C55" s="18" t="n"/>
-      <c r="D55" s="34" t="n"/>
-      <c r="E55" s="34" t="n"/>
-      <c r="F55" s="35" t="n"/>
-      <c r="G55" s="35" t="n"/>
-      <c r="H55" s="35" t="n"/>
-      <c r="I55" s="35" t="n"/>
-      <c r="J55" s="35" t="n"/>
-      <c r="K55" s="35" t="n"/>
-      <c r="L55" s="36">
+      <c r="D55" s="35" t="n"/>
+      <c r="E55" s="35" t="n"/>
+      <c r="F55" s="36" t="n"/>
+      <c r="G55" s="36" t="n"/>
+      <c r="H55" s="36" t="n"/>
+      <c r="I55" s="36" t="n"/>
+      <c r="J55" s="36" t="n"/>
+      <c r="K55" s="36" t="n"/>
+      <c r="L55" s="37">
         <f>IF($A55="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F55:$K55))</f>
         <v/>
       </c>
@@ -5773,15 +5939,15 @@
       <c r="A56" s="16" t="n"/>
       <c r="B56" s="16" t="n"/>
       <c r="C56" s="18" t="n"/>
-      <c r="D56" s="34" t="n"/>
-      <c r="E56" s="34" t="n"/>
-      <c r="F56" s="35" t="n"/>
-      <c r="G56" s="35" t="n"/>
-      <c r="H56" s="35" t="n"/>
-      <c r="I56" s="35" t="n"/>
-      <c r="J56" s="35" t="n"/>
-      <c r="K56" s="35" t="n"/>
-      <c r="L56" s="36">
+      <c r="D56" s="35" t="n"/>
+      <c r="E56" s="35" t="n"/>
+      <c r="F56" s="36" t="n"/>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="36" t="n"/>
+      <c r="I56" s="36" t="n"/>
+      <c r="J56" s="36" t="n"/>
+      <c r="K56" s="36" t="n"/>
+      <c r="L56" s="37">
         <f>IF($A56="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F56:$K56))</f>
         <v/>
       </c>
@@ -5818,15 +5984,15 @@
       <c r="A57" s="16" t="n"/>
       <c r="B57" s="16" t="n"/>
       <c r="C57" s="18" t="n"/>
-      <c r="D57" s="34" t="n"/>
-      <c r="E57" s="34" t="n"/>
-      <c r="F57" s="35" t="n"/>
-      <c r="G57" s="35" t="n"/>
-      <c r="H57" s="35" t="n"/>
-      <c r="I57" s="35" t="n"/>
-      <c r="J57" s="35" t="n"/>
-      <c r="K57" s="35" t="n"/>
-      <c r="L57" s="36">
+      <c r="D57" s="35" t="n"/>
+      <c r="E57" s="35" t="n"/>
+      <c r="F57" s="36" t="n"/>
+      <c r="G57" s="36" t="n"/>
+      <c r="H57" s="36" t="n"/>
+      <c r="I57" s="36" t="n"/>
+      <c r="J57" s="36" t="n"/>
+      <c r="K57" s="36" t="n"/>
+      <c r="L57" s="37">
         <f>IF($A57="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F57:$K57))</f>
         <v/>
       </c>
@@ -5863,15 +6029,15 @@
       <c r="A58" s="16" t="n"/>
       <c r="B58" s="16" t="n"/>
       <c r="C58" s="18" t="n"/>
-      <c r="D58" s="34" t="n"/>
-      <c r="E58" s="34" t="n"/>
-      <c r="F58" s="35" t="n"/>
-      <c r="G58" s="35" t="n"/>
-      <c r="H58" s="35" t="n"/>
-      <c r="I58" s="35" t="n"/>
-      <c r="J58" s="35" t="n"/>
-      <c r="K58" s="35" t="n"/>
-      <c r="L58" s="36">
+      <c r="D58" s="35" t="n"/>
+      <c r="E58" s="35" t="n"/>
+      <c r="F58" s="36" t="n"/>
+      <c r="G58" s="36" t="n"/>
+      <c r="H58" s="36" t="n"/>
+      <c r="I58" s="36" t="n"/>
+      <c r="J58" s="36" t="n"/>
+      <c r="K58" s="36" t="n"/>
+      <c r="L58" s="37">
         <f>IF($A58="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F58:$K58))</f>
         <v/>
       </c>
@@ -5908,15 +6074,15 @@
       <c r="A59" s="16" t="n"/>
       <c r="B59" s="16" t="n"/>
       <c r="C59" s="18" t="n"/>
-      <c r="D59" s="34" t="n"/>
-      <c r="E59" s="34" t="n"/>
-      <c r="F59" s="35" t="n"/>
-      <c r="G59" s="35" t="n"/>
-      <c r="H59" s="35" t="n"/>
-      <c r="I59" s="35" t="n"/>
-      <c r="J59" s="35" t="n"/>
-      <c r="K59" s="35" t="n"/>
-      <c r="L59" s="36">
+      <c r="D59" s="35" t="n"/>
+      <c r="E59" s="35" t="n"/>
+      <c r="F59" s="36" t="n"/>
+      <c r="G59" s="36" t="n"/>
+      <c r="H59" s="36" t="n"/>
+      <c r="I59" s="36" t="n"/>
+      <c r="J59" s="36" t="n"/>
+      <c r="K59" s="36" t="n"/>
+      <c r="L59" s="37">
         <f>IF($A59="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F59:$K59))</f>
         <v/>
       </c>
@@ -5953,15 +6119,15 @@
       <c r="A60" s="16" t="n"/>
       <c r="B60" s="16" t="n"/>
       <c r="C60" s="18" t="n"/>
-      <c r="D60" s="34" t="n"/>
-      <c r="E60" s="34" t="n"/>
-      <c r="F60" s="35" t="n"/>
-      <c r="G60" s="35" t="n"/>
-      <c r="H60" s="35" t="n"/>
-      <c r="I60" s="35" t="n"/>
-      <c r="J60" s="35" t="n"/>
-      <c r="K60" s="35" t="n"/>
-      <c r="L60" s="36">
+      <c r="D60" s="35" t="n"/>
+      <c r="E60" s="35" t="n"/>
+      <c r="F60" s="36" t="n"/>
+      <c r="G60" s="36" t="n"/>
+      <c r="H60" s="36" t="n"/>
+      <c r="I60" s="36" t="n"/>
+      <c r="J60" s="36" t="n"/>
+      <c r="K60" s="36" t="n"/>
+      <c r="L60" s="37">
         <f>IF($A60="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F60:$K60))</f>
         <v/>
       </c>
@@ -5998,15 +6164,15 @@
       <c r="A61" s="16" t="n"/>
       <c r="B61" s="16" t="n"/>
       <c r="C61" s="18" t="n"/>
-      <c r="D61" s="34" t="n"/>
-      <c r="E61" s="34" t="n"/>
-      <c r="F61" s="35" t="n"/>
-      <c r="G61" s="35" t="n"/>
-      <c r="H61" s="35" t="n"/>
-      <c r="I61" s="35" t="n"/>
-      <c r="J61" s="35" t="n"/>
-      <c r="K61" s="35" t="n"/>
-      <c r="L61" s="36">
+      <c r="D61" s="35" t="n"/>
+      <c r="E61" s="35" t="n"/>
+      <c r="F61" s="36" t="n"/>
+      <c r="G61" s="36" t="n"/>
+      <c r="H61" s="36" t="n"/>
+      <c r="I61" s="36" t="n"/>
+      <c r="J61" s="36" t="n"/>
+      <c r="K61" s="36" t="n"/>
+      <c r="L61" s="37">
         <f>IF($A61="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F61:$K61))</f>
         <v/>
       </c>
@@ -6043,15 +6209,15 @@
       <c r="A62" s="16" t="n"/>
       <c r="B62" s="16" t="n"/>
       <c r="C62" s="18" t="n"/>
-      <c r="D62" s="34" t="n"/>
-      <c r="E62" s="34" t="n"/>
-      <c r="F62" s="35" t="n"/>
-      <c r="G62" s="35" t="n"/>
-      <c r="H62" s="35" t="n"/>
-      <c r="I62" s="35" t="n"/>
-      <c r="J62" s="35" t="n"/>
-      <c r="K62" s="35" t="n"/>
-      <c r="L62" s="36">
+      <c r="D62" s="35" t="n"/>
+      <c r="E62" s="35" t="n"/>
+      <c r="F62" s="36" t="n"/>
+      <c r="G62" s="36" t="n"/>
+      <c r="H62" s="36" t="n"/>
+      <c r="I62" s="36" t="n"/>
+      <c r="J62" s="36" t="n"/>
+      <c r="K62" s="36" t="n"/>
+      <c r="L62" s="37">
         <f>IF($A62="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F62:$K62))</f>
         <v/>
       </c>
@@ -6088,15 +6254,15 @@
       <c r="A63" s="16" t="n"/>
       <c r="B63" s="16" t="n"/>
       <c r="C63" s="18" t="n"/>
-      <c r="D63" s="34" t="n"/>
-      <c r="E63" s="34" t="n"/>
-      <c r="F63" s="35" t="n"/>
-      <c r="G63" s="35" t="n"/>
-      <c r="H63" s="35" t="n"/>
-      <c r="I63" s="35" t="n"/>
-      <c r="J63" s="35" t="n"/>
-      <c r="K63" s="35" t="n"/>
-      <c r="L63" s="36">
+      <c r="D63" s="35" t="n"/>
+      <c r="E63" s="35" t="n"/>
+      <c r="F63" s="36" t="n"/>
+      <c r="G63" s="36" t="n"/>
+      <c r="H63" s="36" t="n"/>
+      <c r="I63" s="36" t="n"/>
+      <c r="J63" s="36" t="n"/>
+      <c r="K63" s="36" t="n"/>
+      <c r="L63" s="37">
         <f>IF($A63="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F63:$K63))</f>
         <v/>
       </c>
@@ -6133,15 +6299,15 @@
       <c r="A64" s="16" t="n"/>
       <c r="B64" s="16" t="n"/>
       <c r="C64" s="18" t="n"/>
-      <c r="D64" s="34" t="n"/>
-      <c r="E64" s="34" t="n"/>
-      <c r="F64" s="35" t="n"/>
-      <c r="G64" s="35" t="n"/>
-      <c r="H64" s="35" t="n"/>
-      <c r="I64" s="35" t="n"/>
-      <c r="J64" s="35" t="n"/>
-      <c r="K64" s="35" t="n"/>
-      <c r="L64" s="36">
+      <c r="D64" s="35" t="n"/>
+      <c r="E64" s="35" t="n"/>
+      <c r="F64" s="36" t="n"/>
+      <c r="G64" s="36" t="n"/>
+      <c r="H64" s="36" t="n"/>
+      <c r="I64" s="36" t="n"/>
+      <c r="J64" s="36" t="n"/>
+      <c r="K64" s="36" t="n"/>
+      <c r="L64" s="37">
         <f>IF($A64="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F64:$K64))</f>
         <v/>
       </c>
@@ -6178,15 +6344,15 @@
       <c r="A65" s="16" t="n"/>
       <c r="B65" s="16" t="n"/>
       <c r="C65" s="18" t="n"/>
-      <c r="D65" s="34" t="n"/>
-      <c r="E65" s="34" t="n"/>
-      <c r="F65" s="35" t="n"/>
-      <c r="G65" s="35" t="n"/>
-      <c r="H65" s="35" t="n"/>
-      <c r="I65" s="35" t="n"/>
-      <c r="J65" s="35" t="n"/>
-      <c r="K65" s="35" t="n"/>
-      <c r="L65" s="36">
+      <c r="D65" s="35" t="n"/>
+      <c r="E65" s="35" t="n"/>
+      <c r="F65" s="36" t="n"/>
+      <c r="G65" s="36" t="n"/>
+      <c r="H65" s="36" t="n"/>
+      <c r="I65" s="36" t="n"/>
+      <c r="J65" s="36" t="n"/>
+      <c r="K65" s="36" t="n"/>
+      <c r="L65" s="37">
         <f>IF($A65="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F65:$K65))</f>
         <v/>
       </c>
@@ -6223,15 +6389,15 @@
       <c r="A66" s="16" t="n"/>
       <c r="B66" s="16" t="n"/>
       <c r="C66" s="18" t="n"/>
-      <c r="D66" s="34" t="n"/>
-      <c r="E66" s="34" t="n"/>
-      <c r="F66" s="35" t="n"/>
-      <c r="G66" s="35" t="n"/>
-      <c r="H66" s="35" t="n"/>
-      <c r="I66" s="35" t="n"/>
-      <c r="J66" s="35" t="n"/>
-      <c r="K66" s="35" t="n"/>
-      <c r="L66" s="36">
+      <c r="D66" s="35" t="n"/>
+      <c r="E66" s="35" t="n"/>
+      <c r="F66" s="36" t="n"/>
+      <c r="G66" s="36" t="n"/>
+      <c r="H66" s="36" t="n"/>
+      <c r="I66" s="36" t="n"/>
+      <c r="J66" s="36" t="n"/>
+      <c r="K66" s="36" t="n"/>
+      <c r="L66" s="37">
         <f>IF($A66="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F66:$K66))</f>
         <v/>
       </c>
@@ -6268,15 +6434,15 @@
       <c r="A67" s="16" t="n"/>
       <c r="B67" s="16" t="n"/>
       <c r="C67" s="18" t="n"/>
-      <c r="D67" s="34" t="n"/>
-      <c r="E67" s="34" t="n"/>
-      <c r="F67" s="35" t="n"/>
-      <c r="G67" s="35" t="n"/>
-      <c r="H67" s="35" t="n"/>
-      <c r="I67" s="35" t="n"/>
-      <c r="J67" s="35" t="n"/>
-      <c r="K67" s="35" t="n"/>
-      <c r="L67" s="36">
+      <c r="D67" s="35" t="n"/>
+      <c r="E67" s="35" t="n"/>
+      <c r="F67" s="36" t="n"/>
+      <c r="G67" s="36" t="n"/>
+      <c r="H67" s="36" t="n"/>
+      <c r="I67" s="36" t="n"/>
+      <c r="J67" s="36" t="n"/>
+      <c r="K67" s="36" t="n"/>
+      <c r="L67" s="37">
         <f>IF($A67="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F67:$K67))</f>
         <v/>
       </c>
@@ -6313,15 +6479,15 @@
       <c r="A68" s="16" t="n"/>
       <c r="B68" s="16" t="n"/>
       <c r="C68" s="18" t="n"/>
-      <c r="D68" s="34" t="n"/>
-      <c r="E68" s="34" t="n"/>
-      <c r="F68" s="35" t="n"/>
-      <c r="G68" s="35" t="n"/>
-      <c r="H68" s="35" t="n"/>
-      <c r="I68" s="35" t="n"/>
-      <c r="J68" s="35" t="n"/>
-      <c r="K68" s="35" t="n"/>
-      <c r="L68" s="36">
+      <c r="D68" s="35" t="n"/>
+      <c r="E68" s="35" t="n"/>
+      <c r="F68" s="36" t="n"/>
+      <c r="G68" s="36" t="n"/>
+      <c r="H68" s="36" t="n"/>
+      <c r="I68" s="36" t="n"/>
+      <c r="J68" s="36" t="n"/>
+      <c r="K68" s="36" t="n"/>
+      <c r="L68" s="37">
         <f>IF($A68="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F68:$K68))</f>
         <v/>
       </c>
@@ -6358,15 +6524,15 @@
       <c r="A69" s="16" t="n"/>
       <c r="B69" s="16" t="n"/>
       <c r="C69" s="18" t="n"/>
-      <c r="D69" s="34" t="n"/>
-      <c r="E69" s="34" t="n"/>
-      <c r="F69" s="35" t="n"/>
-      <c r="G69" s="35" t="n"/>
-      <c r="H69" s="35" t="n"/>
-      <c r="I69" s="35" t="n"/>
-      <c r="J69" s="35" t="n"/>
-      <c r="K69" s="35" t="n"/>
-      <c r="L69" s="36">
+      <c r="D69" s="35" t="n"/>
+      <c r="E69" s="35" t="n"/>
+      <c r="F69" s="36" t="n"/>
+      <c r="G69" s="36" t="n"/>
+      <c r="H69" s="36" t="n"/>
+      <c r="I69" s="36" t="n"/>
+      <c r="J69" s="36" t="n"/>
+      <c r="K69" s="36" t="n"/>
+      <c r="L69" s="37">
         <f>IF($A69="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F69:$K69))</f>
         <v/>
       </c>
@@ -6403,15 +6569,15 @@
       <c r="A70" s="16" t="n"/>
       <c r="B70" s="16" t="n"/>
       <c r="C70" s="18" t="n"/>
-      <c r="D70" s="34" t="n"/>
-      <c r="E70" s="34" t="n"/>
-      <c r="F70" s="35" t="n"/>
-      <c r="G70" s="35" t="n"/>
-      <c r="H70" s="35" t="n"/>
-      <c r="I70" s="35" t="n"/>
-      <c r="J70" s="35" t="n"/>
-      <c r="K70" s="35" t="n"/>
-      <c r="L70" s="36">
+      <c r="D70" s="35" t="n"/>
+      <c r="E70" s="35" t="n"/>
+      <c r="F70" s="36" t="n"/>
+      <c r="G70" s="36" t="n"/>
+      <c r="H70" s="36" t="n"/>
+      <c r="I70" s="36" t="n"/>
+      <c r="J70" s="36" t="n"/>
+      <c r="K70" s="36" t="n"/>
+      <c r="L70" s="37">
         <f>IF($A70="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F70:$K70))</f>
         <v/>
       </c>
@@ -6448,15 +6614,15 @@
       <c r="A71" s="16" t="n"/>
       <c r="B71" s="16" t="n"/>
       <c r="C71" s="18" t="n"/>
-      <c r="D71" s="34" t="n"/>
-      <c r="E71" s="34" t="n"/>
-      <c r="F71" s="35" t="n"/>
-      <c r="G71" s="35" t="n"/>
-      <c r="H71" s="35" t="n"/>
-      <c r="I71" s="35" t="n"/>
-      <c r="J71" s="35" t="n"/>
-      <c r="K71" s="35" t="n"/>
-      <c r="L71" s="36">
+      <c r="D71" s="35" t="n"/>
+      <c r="E71" s="35" t="n"/>
+      <c r="F71" s="36" t="n"/>
+      <c r="G71" s="36" t="n"/>
+      <c r="H71" s="36" t="n"/>
+      <c r="I71" s="36" t="n"/>
+      <c r="J71" s="36" t="n"/>
+      <c r="K71" s="36" t="n"/>
+      <c r="L71" s="37">
         <f>IF($A71="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F71:$K71))</f>
         <v/>
       </c>
@@ -6493,15 +6659,15 @@
       <c r="A72" s="16" t="n"/>
       <c r="B72" s="16" t="n"/>
       <c r="C72" s="18" t="n"/>
-      <c r="D72" s="34" t="n"/>
-      <c r="E72" s="34" t="n"/>
-      <c r="F72" s="35" t="n"/>
-      <c r="G72" s="35" t="n"/>
-      <c r="H72" s="35" t="n"/>
-      <c r="I72" s="35" t="n"/>
-      <c r="J72" s="35" t="n"/>
-      <c r="K72" s="35" t="n"/>
-      <c r="L72" s="36">
+      <c r="D72" s="35" t="n"/>
+      <c r="E72" s="35" t="n"/>
+      <c r="F72" s="36" t="n"/>
+      <c r="G72" s="36" t="n"/>
+      <c r="H72" s="36" t="n"/>
+      <c r="I72" s="36" t="n"/>
+      <c r="J72" s="36" t="n"/>
+      <c r="K72" s="36" t="n"/>
+      <c r="L72" s="37">
         <f>IF($A72="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F72:$K72))</f>
         <v/>
       </c>
@@ -6538,15 +6704,15 @@
       <c r="A73" s="16" t="n"/>
       <c r="B73" s="16" t="n"/>
       <c r="C73" s="18" t="n"/>
-      <c r="D73" s="34" t="n"/>
-      <c r="E73" s="34" t="n"/>
-      <c r="F73" s="35" t="n"/>
-      <c r="G73" s="35" t="n"/>
-      <c r="H73" s="35" t="n"/>
-      <c r="I73" s="35" t="n"/>
-      <c r="J73" s="35" t="n"/>
-      <c r="K73" s="35" t="n"/>
-      <c r="L73" s="36">
+      <c r="D73" s="35" t="n"/>
+      <c r="E73" s="35" t="n"/>
+      <c r="F73" s="36" t="n"/>
+      <c r="G73" s="36" t="n"/>
+      <c r="H73" s="36" t="n"/>
+      <c r="I73" s="36" t="n"/>
+      <c r="J73" s="36" t="n"/>
+      <c r="K73" s="36" t="n"/>
+      <c r="L73" s="37">
         <f>IF($A73="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F73:$K73))</f>
         <v/>
       </c>
@@ -6583,15 +6749,15 @@
       <c r="A74" s="16" t="n"/>
       <c r="B74" s="16" t="n"/>
       <c r="C74" s="18" t="n"/>
-      <c r="D74" s="34" t="n"/>
-      <c r="E74" s="34" t="n"/>
-      <c r="F74" s="35" t="n"/>
-      <c r="G74" s="35" t="n"/>
-      <c r="H74" s="35" t="n"/>
-      <c r="I74" s="35" t="n"/>
-      <c r="J74" s="35" t="n"/>
-      <c r="K74" s="35" t="n"/>
-      <c r="L74" s="36">
+      <c r="D74" s="35" t="n"/>
+      <c r="E74" s="35" t="n"/>
+      <c r="F74" s="36" t="n"/>
+      <c r="G74" s="36" t="n"/>
+      <c r="H74" s="36" t="n"/>
+      <c r="I74" s="36" t="n"/>
+      <c r="J74" s="36" t="n"/>
+      <c r="K74" s="36" t="n"/>
+      <c r="L74" s="37">
         <f>IF($A74="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F74:$K74))</f>
         <v/>
       </c>
@@ -6628,15 +6794,15 @@
       <c r="A75" s="16" t="n"/>
       <c r="B75" s="16" t="n"/>
       <c r="C75" s="18" t="n"/>
-      <c r="D75" s="34" t="n"/>
-      <c r="E75" s="34" t="n"/>
-      <c r="F75" s="35" t="n"/>
-      <c r="G75" s="35" t="n"/>
-      <c r="H75" s="35" t="n"/>
-      <c r="I75" s="35" t="n"/>
-      <c r="J75" s="35" t="n"/>
-      <c r="K75" s="35" t="n"/>
-      <c r="L75" s="36">
+      <c r="D75" s="35" t="n"/>
+      <c r="E75" s="35" t="n"/>
+      <c r="F75" s="36" t="n"/>
+      <c r="G75" s="36" t="n"/>
+      <c r="H75" s="36" t="n"/>
+      <c r="I75" s="36" t="n"/>
+      <c r="J75" s="36" t="n"/>
+      <c r="K75" s="36" t="n"/>
+      <c r="L75" s="37">
         <f>IF($A75="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F75:$K75))</f>
         <v/>
       </c>
@@ -6673,15 +6839,15 @@
       <c r="A76" s="16" t="n"/>
       <c r="B76" s="16" t="n"/>
       <c r="C76" s="18" t="n"/>
-      <c r="D76" s="34" t="n"/>
-      <c r="E76" s="34" t="n"/>
-      <c r="F76" s="35" t="n"/>
-      <c r="G76" s="35" t="n"/>
-      <c r="H76" s="35" t="n"/>
-      <c r="I76" s="35" t="n"/>
-      <c r="J76" s="35" t="n"/>
-      <c r="K76" s="35" t="n"/>
-      <c r="L76" s="36">
+      <c r="D76" s="35" t="n"/>
+      <c r="E76" s="35" t="n"/>
+      <c r="F76" s="36" t="n"/>
+      <c r="G76" s="36" t="n"/>
+      <c r="H76" s="36" t="n"/>
+      <c r="I76" s="36" t="n"/>
+      <c r="J76" s="36" t="n"/>
+      <c r="K76" s="36" t="n"/>
+      <c r="L76" s="37">
         <f>IF($A76="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F76:$K76))</f>
         <v/>
       </c>
@@ -6718,15 +6884,15 @@
       <c r="A77" s="16" t="n"/>
       <c r="B77" s="16" t="n"/>
       <c r="C77" s="18" t="n"/>
-      <c r="D77" s="34" t="n"/>
-      <c r="E77" s="34" t="n"/>
-      <c r="F77" s="35" t="n"/>
-      <c r="G77" s="35" t="n"/>
-      <c r="H77" s="35" t="n"/>
-      <c r="I77" s="35" t="n"/>
-      <c r="J77" s="35" t="n"/>
-      <c r="K77" s="35" t="n"/>
-      <c r="L77" s="36">
+      <c r="D77" s="35" t="n"/>
+      <c r="E77" s="35" t="n"/>
+      <c r="F77" s="36" t="n"/>
+      <c r="G77" s="36" t="n"/>
+      <c r="H77" s="36" t="n"/>
+      <c r="I77" s="36" t="n"/>
+      <c r="J77" s="36" t="n"/>
+      <c r="K77" s="36" t="n"/>
+      <c r="L77" s="37">
         <f>IF($A77="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F77:$K77))</f>
         <v/>
       </c>
@@ -6763,15 +6929,15 @@
       <c r="A78" s="16" t="n"/>
       <c r="B78" s="16" t="n"/>
       <c r="C78" s="18" t="n"/>
-      <c r="D78" s="34" t="n"/>
-      <c r="E78" s="34" t="n"/>
-      <c r="F78" s="35" t="n"/>
-      <c r="G78" s="35" t="n"/>
-      <c r="H78" s="35" t="n"/>
-      <c r="I78" s="35" t="n"/>
-      <c r="J78" s="35" t="n"/>
-      <c r="K78" s="35" t="n"/>
-      <c r="L78" s="36">
+      <c r="D78" s="35" t="n"/>
+      <c r="E78" s="35" t="n"/>
+      <c r="F78" s="36" t="n"/>
+      <c r="G78" s="36" t="n"/>
+      <c r="H78" s="36" t="n"/>
+      <c r="I78" s="36" t="n"/>
+      <c r="J78" s="36" t="n"/>
+      <c r="K78" s="36" t="n"/>
+      <c r="L78" s="37">
         <f>IF($A78="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F78:$K78))</f>
         <v/>
       </c>
@@ -6808,15 +6974,15 @@
       <c r="A79" s="16" t="n"/>
       <c r="B79" s="16" t="n"/>
       <c r="C79" s="18" t="n"/>
-      <c r="D79" s="34" t="n"/>
-      <c r="E79" s="34" t="n"/>
-      <c r="F79" s="35" t="n"/>
-      <c r="G79" s="35" t="n"/>
-      <c r="H79" s="35" t="n"/>
-      <c r="I79" s="35" t="n"/>
-      <c r="J79" s="35" t="n"/>
-      <c r="K79" s="35" t="n"/>
-      <c r="L79" s="36">
+      <c r="D79" s="35" t="n"/>
+      <c r="E79" s="35" t="n"/>
+      <c r="F79" s="36" t="n"/>
+      <c r="G79" s="36" t="n"/>
+      <c r="H79" s="36" t="n"/>
+      <c r="I79" s="36" t="n"/>
+      <c r="J79" s="36" t="n"/>
+      <c r="K79" s="36" t="n"/>
+      <c r="L79" s="37">
         <f>IF($A79="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F79:$K79))</f>
         <v/>
       </c>
@@ -6853,15 +7019,15 @@
       <c r="A80" s="16" t="n"/>
       <c r="B80" s="16" t="n"/>
       <c r="C80" s="18" t="n"/>
-      <c r="D80" s="34" t="n"/>
-      <c r="E80" s="34" t="n"/>
-      <c r="F80" s="35" t="n"/>
-      <c r="G80" s="35" t="n"/>
-      <c r="H80" s="35" t="n"/>
-      <c r="I80" s="35" t="n"/>
-      <c r="J80" s="35" t="n"/>
-      <c r="K80" s="35" t="n"/>
-      <c r="L80" s="36">
+      <c r="D80" s="35" t="n"/>
+      <c r="E80" s="35" t="n"/>
+      <c r="F80" s="36" t="n"/>
+      <c r="G80" s="36" t="n"/>
+      <c r="H80" s="36" t="n"/>
+      <c r="I80" s="36" t="n"/>
+      <c r="J80" s="36" t="n"/>
+      <c r="K80" s="36" t="n"/>
+      <c r="L80" s="37">
         <f>IF($A80="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F80:$K80))</f>
         <v/>
       </c>
@@ -6898,15 +7064,15 @@
       <c r="A81" s="16" t="n"/>
       <c r="B81" s="16" t="n"/>
       <c r="C81" s="18" t="n"/>
-      <c r="D81" s="34" t="n"/>
-      <c r="E81" s="34" t="n"/>
-      <c r="F81" s="35" t="n"/>
-      <c r="G81" s="35" t="n"/>
-      <c r="H81" s="35" t="n"/>
-      <c r="I81" s="35" t="n"/>
-      <c r="J81" s="35" t="n"/>
-      <c r="K81" s="35" t="n"/>
-      <c r="L81" s="36">
+      <c r="D81" s="35" t="n"/>
+      <c r="E81" s="35" t="n"/>
+      <c r="F81" s="36" t="n"/>
+      <c r="G81" s="36" t="n"/>
+      <c r="H81" s="36" t="n"/>
+      <c r="I81" s="36" t="n"/>
+      <c r="J81" s="36" t="n"/>
+      <c r="K81" s="36" t="n"/>
+      <c r="L81" s="37">
         <f>IF($A81="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F81:$K81))</f>
         <v/>
       </c>
@@ -6943,15 +7109,15 @@
       <c r="A82" s="16" t="n"/>
       <c r="B82" s="16" t="n"/>
       <c r="C82" s="18" t="n"/>
-      <c r="D82" s="34" t="n"/>
-      <c r="E82" s="34" t="n"/>
-      <c r="F82" s="35" t="n"/>
-      <c r="G82" s="35" t="n"/>
-      <c r="H82" s="35" t="n"/>
-      <c r="I82" s="35" t="n"/>
-      <c r="J82" s="35" t="n"/>
-      <c r="K82" s="35" t="n"/>
-      <c r="L82" s="36">
+      <c r="D82" s="35" t="n"/>
+      <c r="E82" s="35" t="n"/>
+      <c r="F82" s="36" t="n"/>
+      <c r="G82" s="36" t="n"/>
+      <c r="H82" s="36" t="n"/>
+      <c r="I82" s="36" t="n"/>
+      <c r="J82" s="36" t="n"/>
+      <c r="K82" s="36" t="n"/>
+      <c r="L82" s="37">
         <f>IF($A82="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F82:$K82))</f>
         <v/>
       </c>
@@ -6988,15 +7154,15 @@
       <c r="A83" s="16" t="n"/>
       <c r="B83" s="16" t="n"/>
       <c r="C83" s="18" t="n"/>
-      <c r="D83" s="34" t="n"/>
-      <c r="E83" s="34" t="n"/>
-      <c r="F83" s="35" t="n"/>
-      <c r="G83" s="35" t="n"/>
-      <c r="H83" s="35" t="n"/>
-      <c r="I83" s="35" t="n"/>
-      <c r="J83" s="35" t="n"/>
-      <c r="K83" s="35" t="n"/>
-      <c r="L83" s="36">
+      <c r="D83" s="35" t="n"/>
+      <c r="E83" s="35" t="n"/>
+      <c r="F83" s="36" t="n"/>
+      <c r="G83" s="36" t="n"/>
+      <c r="H83" s="36" t="n"/>
+      <c r="I83" s="36" t="n"/>
+      <c r="J83" s="36" t="n"/>
+      <c r="K83" s="36" t="n"/>
+      <c r="L83" s="37">
         <f>IF($A83="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F83:$K83))</f>
         <v/>
       </c>
@@ -7033,15 +7199,15 @@
       <c r="A84" s="16" t="n"/>
       <c r="B84" s="16" t="n"/>
       <c r="C84" s="18" t="n"/>
-      <c r="D84" s="34" t="n"/>
-      <c r="E84" s="34" t="n"/>
-      <c r="F84" s="35" t="n"/>
-      <c r="G84" s="35" t="n"/>
-      <c r="H84" s="35" t="n"/>
-      <c r="I84" s="35" t="n"/>
-      <c r="J84" s="35" t="n"/>
-      <c r="K84" s="35" t="n"/>
-      <c r="L84" s="36">
+      <c r="D84" s="35" t="n"/>
+      <c r="E84" s="35" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="36" t="n"/>
+      <c r="H84" s="36" t="n"/>
+      <c r="I84" s="36" t="n"/>
+      <c r="J84" s="36" t="n"/>
+      <c r="K84" s="36" t="n"/>
+      <c r="L84" s="37">
         <f>IF($A84="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F84:$K84))</f>
         <v/>
       </c>
@@ -7078,15 +7244,15 @@
       <c r="A85" s="16" t="n"/>
       <c r="B85" s="16" t="n"/>
       <c r="C85" s="18" t="n"/>
-      <c r="D85" s="34" t="n"/>
-      <c r="E85" s="34" t="n"/>
-      <c r="F85" s="35" t="n"/>
-      <c r="G85" s="35" t="n"/>
-      <c r="H85" s="35" t="n"/>
-      <c r="I85" s="35" t="n"/>
-      <c r="J85" s="35" t="n"/>
-      <c r="K85" s="35" t="n"/>
-      <c r="L85" s="36">
+      <c r="D85" s="35" t="n"/>
+      <c r="E85" s="35" t="n"/>
+      <c r="F85" s="36" t="n"/>
+      <c r="G85" s="36" t="n"/>
+      <c r="H85" s="36" t="n"/>
+      <c r="I85" s="36" t="n"/>
+      <c r="J85" s="36" t="n"/>
+      <c r="K85" s="36" t="n"/>
+      <c r="L85" s="37">
         <f>IF($A85="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F85:$K85))</f>
         <v/>
       </c>
@@ -7123,15 +7289,15 @@
       <c r="A86" s="16" t="n"/>
       <c r="B86" s="16" t="n"/>
       <c r="C86" s="18" t="n"/>
-      <c r="D86" s="34" t="n"/>
-      <c r="E86" s="34" t="n"/>
-      <c r="F86" s="35" t="n"/>
-      <c r="G86" s="35" t="n"/>
-      <c r="H86" s="35" t="n"/>
-      <c r="I86" s="35" t="n"/>
-      <c r="J86" s="35" t="n"/>
-      <c r="K86" s="35" t="n"/>
-      <c r="L86" s="36">
+      <c r="D86" s="35" t="n"/>
+      <c r="E86" s="35" t="n"/>
+      <c r="F86" s="36" t="n"/>
+      <c r="G86" s="36" t="n"/>
+      <c r="H86" s="36" t="n"/>
+      <c r="I86" s="36" t="n"/>
+      <c r="J86" s="36" t="n"/>
+      <c r="K86" s="36" t="n"/>
+      <c r="L86" s="37">
         <f>IF($A86="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F86:$K86))</f>
         <v/>
       </c>
@@ -7168,15 +7334,15 @@
       <c r="A87" s="16" t="n"/>
       <c r="B87" s="16" t="n"/>
       <c r="C87" s="18" t="n"/>
-      <c r="D87" s="34" t="n"/>
-      <c r="E87" s="34" t="n"/>
-      <c r="F87" s="35" t="n"/>
-      <c r="G87" s="35" t="n"/>
-      <c r="H87" s="35" t="n"/>
-      <c r="I87" s="35" t="n"/>
-      <c r="J87" s="35" t="n"/>
-      <c r="K87" s="35" t="n"/>
-      <c r="L87" s="36">
+      <c r="D87" s="35" t="n"/>
+      <c r="E87" s="35" t="n"/>
+      <c r="F87" s="36" t="n"/>
+      <c r="G87" s="36" t="n"/>
+      <c r="H87" s="36" t="n"/>
+      <c r="I87" s="36" t="n"/>
+      <c r="J87" s="36" t="n"/>
+      <c r="K87" s="36" t="n"/>
+      <c r="L87" s="37">
         <f>IF($A87="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F87:$K87))</f>
         <v/>
       </c>
@@ -7213,15 +7379,15 @@
       <c r="A88" s="16" t="n"/>
       <c r="B88" s="16" t="n"/>
       <c r="C88" s="18" t="n"/>
-      <c r="D88" s="34" t="n"/>
-      <c r="E88" s="34" t="n"/>
-      <c r="F88" s="35" t="n"/>
-      <c r="G88" s="35" t="n"/>
-      <c r="H88" s="35" t="n"/>
-      <c r="I88" s="35" t="n"/>
-      <c r="J88" s="35" t="n"/>
-      <c r="K88" s="35" t="n"/>
-      <c r="L88" s="36">
+      <c r="D88" s="35" t="n"/>
+      <c r="E88" s="35" t="n"/>
+      <c r="F88" s="36" t="n"/>
+      <c r="G88" s="36" t="n"/>
+      <c r="H88" s="36" t="n"/>
+      <c r="I88" s="36" t="n"/>
+      <c r="J88" s="36" t="n"/>
+      <c r="K88" s="36" t="n"/>
+      <c r="L88" s="37">
         <f>IF($A88="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F88:$K88))</f>
         <v/>
       </c>
@@ -7258,15 +7424,15 @@
       <c r="A89" s="16" t="n"/>
       <c r="B89" s="16" t="n"/>
       <c r="C89" s="18" t="n"/>
-      <c r="D89" s="34" t="n"/>
-      <c r="E89" s="34" t="n"/>
-      <c r="F89" s="35" t="n"/>
-      <c r="G89" s="35" t="n"/>
-      <c r="H89" s="35" t="n"/>
-      <c r="I89" s="35" t="n"/>
-      <c r="J89" s="35" t="n"/>
-      <c r="K89" s="35" t="n"/>
-      <c r="L89" s="36">
+      <c r="D89" s="35" t="n"/>
+      <c r="E89" s="35" t="n"/>
+      <c r="F89" s="36" t="n"/>
+      <c r="G89" s="36" t="n"/>
+      <c r="H89" s="36" t="n"/>
+      <c r="I89" s="36" t="n"/>
+      <c r="J89" s="36" t="n"/>
+      <c r="K89" s="36" t="n"/>
+      <c r="L89" s="37">
         <f>IF($A89="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F89:$K89))</f>
         <v/>
       </c>
@@ -7303,15 +7469,15 @@
       <c r="A90" s="16" t="n"/>
       <c r="B90" s="16" t="n"/>
       <c r="C90" s="18" t="n"/>
-      <c r="D90" s="34" t="n"/>
-      <c r="E90" s="34" t="n"/>
-      <c r="F90" s="35" t="n"/>
-      <c r="G90" s="35" t="n"/>
-      <c r="H90" s="35" t="n"/>
-      <c r="I90" s="35" t="n"/>
-      <c r="J90" s="35" t="n"/>
-      <c r="K90" s="35" t="n"/>
-      <c r="L90" s="36">
+      <c r="D90" s="35" t="n"/>
+      <c r="E90" s="35" t="n"/>
+      <c r="F90" s="36" t="n"/>
+      <c r="G90" s="36" t="n"/>
+      <c r="H90" s="36" t="n"/>
+      <c r="I90" s="36" t="n"/>
+      <c r="J90" s="36" t="n"/>
+      <c r="K90" s="36" t="n"/>
+      <c r="L90" s="37">
         <f>IF($A90="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F90:$K90))</f>
         <v/>
       </c>
@@ -7348,15 +7514,15 @@
       <c r="A91" s="16" t="n"/>
       <c r="B91" s="16" t="n"/>
       <c r="C91" s="18" t="n"/>
-      <c r="D91" s="34" t="n"/>
-      <c r="E91" s="34" t="n"/>
-      <c r="F91" s="35" t="n"/>
-      <c r="G91" s="35" t="n"/>
-      <c r="H91" s="35" t="n"/>
-      <c r="I91" s="35" t="n"/>
-      <c r="J91" s="35" t="n"/>
-      <c r="K91" s="35" t="n"/>
-      <c r="L91" s="36">
+      <c r="D91" s="35" t="n"/>
+      <c r="E91" s="35" t="n"/>
+      <c r="F91" s="36" t="n"/>
+      <c r="G91" s="36" t="n"/>
+      <c r="H91" s="36" t="n"/>
+      <c r="I91" s="36" t="n"/>
+      <c r="J91" s="36" t="n"/>
+      <c r="K91" s="36" t="n"/>
+      <c r="L91" s="37">
         <f>IF($A91="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F91:$K91))</f>
         <v/>
       </c>
@@ -7393,15 +7559,15 @@
       <c r="A92" s="16" t="n"/>
       <c r="B92" s="16" t="n"/>
       <c r="C92" s="18" t="n"/>
-      <c r="D92" s="34" t="n"/>
-      <c r="E92" s="34" t="n"/>
-      <c r="F92" s="35" t="n"/>
-      <c r="G92" s="35" t="n"/>
-      <c r="H92" s="35" t="n"/>
-      <c r="I92" s="35" t="n"/>
-      <c r="J92" s="35" t="n"/>
-      <c r="K92" s="35" t="n"/>
-      <c r="L92" s="36">
+      <c r="D92" s="35" t="n"/>
+      <c r="E92" s="35" t="n"/>
+      <c r="F92" s="36" t="n"/>
+      <c r="G92" s="36" t="n"/>
+      <c r="H92" s="36" t="n"/>
+      <c r="I92" s="36" t="n"/>
+      <c r="J92" s="36" t="n"/>
+      <c r="K92" s="36" t="n"/>
+      <c r="L92" s="37">
         <f>IF($A92="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F92:$K92))</f>
         <v/>
       </c>
@@ -7438,15 +7604,15 @@
       <c r="A93" s="16" t="n"/>
       <c r="B93" s="16" t="n"/>
       <c r="C93" s="18" t="n"/>
-      <c r="D93" s="34" t="n"/>
-      <c r="E93" s="34" t="n"/>
-      <c r="F93" s="35" t="n"/>
-      <c r="G93" s="35" t="n"/>
-      <c r="H93" s="35" t="n"/>
-      <c r="I93" s="35" t="n"/>
-      <c r="J93" s="35" t="n"/>
-      <c r="K93" s="35" t="n"/>
-      <c r="L93" s="36">
+      <c r="D93" s="35" t="n"/>
+      <c r="E93" s="35" t="n"/>
+      <c r="F93" s="36" t="n"/>
+      <c r="G93" s="36" t="n"/>
+      <c r="H93" s="36" t="n"/>
+      <c r="I93" s="36" t="n"/>
+      <c r="J93" s="36" t="n"/>
+      <c r="K93" s="36" t="n"/>
+      <c r="L93" s="37">
         <f>IF($A93="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F93:$K93))</f>
         <v/>
       </c>
@@ -7483,15 +7649,15 @@
       <c r="A94" s="16" t="n"/>
       <c r="B94" s="16" t="n"/>
       <c r="C94" s="18" t="n"/>
-      <c r="D94" s="34" t="n"/>
-      <c r="E94" s="34" t="n"/>
-      <c r="F94" s="35" t="n"/>
-      <c r="G94" s="35" t="n"/>
-      <c r="H94" s="35" t="n"/>
-      <c r="I94" s="35" t="n"/>
-      <c r="J94" s="35" t="n"/>
-      <c r="K94" s="35" t="n"/>
-      <c r="L94" s="36">
+      <c r="D94" s="35" t="n"/>
+      <c r="E94" s="35" t="n"/>
+      <c r="F94" s="36" t="n"/>
+      <c r="G94" s="36" t="n"/>
+      <c r="H94" s="36" t="n"/>
+      <c r="I94" s="36" t="n"/>
+      <c r="J94" s="36" t="n"/>
+      <c r="K94" s="36" t="n"/>
+      <c r="L94" s="37">
         <f>IF($A94="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F94:$K94))</f>
         <v/>
       </c>
@@ -7528,15 +7694,15 @@
       <c r="A95" s="16" t="n"/>
       <c r="B95" s="16" t="n"/>
       <c r="C95" s="18" t="n"/>
-      <c r="D95" s="34" t="n"/>
-      <c r="E95" s="34" t="n"/>
-      <c r="F95" s="35" t="n"/>
-      <c r="G95" s="35" t="n"/>
-      <c r="H95" s="35" t="n"/>
-      <c r="I95" s="35" t="n"/>
-      <c r="J95" s="35" t="n"/>
-      <c r="K95" s="35" t="n"/>
-      <c r="L95" s="36">
+      <c r="D95" s="35" t="n"/>
+      <c r="E95" s="35" t="n"/>
+      <c r="F95" s="36" t="n"/>
+      <c r="G95" s="36" t="n"/>
+      <c r="H95" s="36" t="n"/>
+      <c r="I95" s="36" t="n"/>
+      <c r="J95" s="36" t="n"/>
+      <c r="K95" s="36" t="n"/>
+      <c r="L95" s="37">
         <f>IF($A95="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F95:$K95))</f>
         <v/>
       </c>
@@ -7573,15 +7739,15 @@
       <c r="A96" s="16" t="n"/>
       <c r="B96" s="16" t="n"/>
       <c r="C96" s="18" t="n"/>
-      <c r="D96" s="34" t="n"/>
-      <c r="E96" s="34" t="n"/>
-      <c r="F96" s="35" t="n"/>
-      <c r="G96" s="35" t="n"/>
-      <c r="H96" s="35" t="n"/>
-      <c r="I96" s="35" t="n"/>
-      <c r="J96" s="35" t="n"/>
-      <c r="K96" s="35" t="n"/>
-      <c r="L96" s="36">
+      <c r="D96" s="35" t="n"/>
+      <c r="E96" s="35" t="n"/>
+      <c r="F96" s="36" t="n"/>
+      <c r="G96" s="36" t="n"/>
+      <c r="H96" s="36" t="n"/>
+      <c r="I96" s="36" t="n"/>
+      <c r="J96" s="36" t="n"/>
+      <c r="K96" s="36" t="n"/>
+      <c r="L96" s="37">
         <f>IF($A96="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F96:$K96))</f>
         <v/>
       </c>
@@ -7618,15 +7784,15 @@
       <c r="A97" s="16" t="n"/>
       <c r="B97" s="16" t="n"/>
       <c r="C97" s="18" t="n"/>
-      <c r="D97" s="34" t="n"/>
-      <c r="E97" s="34" t="n"/>
-      <c r="F97" s="35" t="n"/>
-      <c r="G97" s="35" t="n"/>
-      <c r="H97" s="35" t="n"/>
-      <c r="I97" s="35" t="n"/>
-      <c r="J97" s="35" t="n"/>
-      <c r="K97" s="35" t="n"/>
-      <c r="L97" s="36">
+      <c r="D97" s="35" t="n"/>
+      <c r="E97" s="35" t="n"/>
+      <c r="F97" s="36" t="n"/>
+      <c r="G97" s="36" t="n"/>
+      <c r="H97" s="36" t="n"/>
+      <c r="I97" s="36" t="n"/>
+      <c r="J97" s="36" t="n"/>
+      <c r="K97" s="36" t="n"/>
+      <c r="L97" s="37">
         <f>IF($A97="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F97:$K97))</f>
         <v/>
       </c>
@@ -7663,15 +7829,15 @@
       <c r="A98" s="16" t="n"/>
       <c r="B98" s="16" t="n"/>
       <c r="C98" s="18" t="n"/>
-      <c r="D98" s="34" t="n"/>
-      <c r="E98" s="34" t="n"/>
-      <c r="F98" s="35" t="n"/>
-      <c r="G98" s="35" t="n"/>
-      <c r="H98" s="35" t="n"/>
-      <c r="I98" s="35" t="n"/>
-      <c r="J98" s="35" t="n"/>
-      <c r="K98" s="35" t="n"/>
-      <c r="L98" s="36">
+      <c r="D98" s="35" t="n"/>
+      <c r="E98" s="35" t="n"/>
+      <c r="F98" s="36" t="n"/>
+      <c r="G98" s="36" t="n"/>
+      <c r="H98" s="36" t="n"/>
+      <c r="I98" s="36" t="n"/>
+      <c r="J98" s="36" t="n"/>
+      <c r="K98" s="36" t="n"/>
+      <c r="L98" s="37">
         <f>IF($A98="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F98:$K98))</f>
         <v/>
       </c>
@@ -7708,15 +7874,15 @@
       <c r="A99" s="16" t="n"/>
       <c r="B99" s="16" t="n"/>
       <c r="C99" s="18" t="n"/>
-      <c r="D99" s="34" t="n"/>
-      <c r="E99" s="34" t="n"/>
-      <c r="F99" s="35" t="n"/>
-      <c r="G99" s="35" t="n"/>
-      <c r="H99" s="35" t="n"/>
-      <c r="I99" s="35" t="n"/>
-      <c r="J99" s="35" t="n"/>
-      <c r="K99" s="35" t="n"/>
-      <c r="L99" s="36">
+      <c r="D99" s="35" t="n"/>
+      <c r="E99" s="35" t="n"/>
+      <c r="F99" s="36" t="n"/>
+      <c r="G99" s="36" t="n"/>
+      <c r="H99" s="36" t="n"/>
+      <c r="I99" s="36" t="n"/>
+      <c r="J99" s="36" t="n"/>
+      <c r="K99" s="36" t="n"/>
+      <c r="L99" s="37">
         <f>IF($A99="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F99:$K99))</f>
         <v/>
       </c>
@@ -7753,15 +7919,15 @@
       <c r="A100" s="16" t="n"/>
       <c r="B100" s="16" t="n"/>
       <c r="C100" s="18" t="n"/>
-      <c r="D100" s="34" t="n"/>
-      <c r="E100" s="34" t="n"/>
-      <c r="F100" s="35" t="n"/>
-      <c r="G100" s="35" t="n"/>
-      <c r="H100" s="35" t="n"/>
-      <c r="I100" s="35" t="n"/>
-      <c r="J100" s="35" t="n"/>
-      <c r="K100" s="35" t="n"/>
-      <c r="L100" s="36">
+      <c r="D100" s="35" t="n"/>
+      <c r="E100" s="35" t="n"/>
+      <c r="F100" s="36" t="n"/>
+      <c r="G100" s="36" t="n"/>
+      <c r="H100" s="36" t="n"/>
+      <c r="I100" s="36" t="n"/>
+      <c r="J100" s="36" t="n"/>
+      <c r="K100" s="36" t="n"/>
+      <c r="L100" s="37">
         <f>IF($A100="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F100:$K100))</f>
         <v/>
       </c>
@@ -7798,15 +7964,15 @@
       <c r="A101" s="16" t="n"/>
       <c r="B101" s="16" t="n"/>
       <c r="C101" s="18" t="n"/>
-      <c r="D101" s="34" t="n"/>
-      <c r="E101" s="34" t="n"/>
-      <c r="F101" s="35" t="n"/>
-      <c r="G101" s="35" t="n"/>
-      <c r="H101" s="35" t="n"/>
-      <c r="I101" s="35" t="n"/>
-      <c r="J101" s="35" t="n"/>
-      <c r="K101" s="35" t="n"/>
-      <c r="L101" s="36">
+      <c r="D101" s="35" t="n"/>
+      <c r="E101" s="35" t="n"/>
+      <c r="F101" s="36" t="n"/>
+      <c r="G101" s="36" t="n"/>
+      <c r="H101" s="36" t="n"/>
+      <c r="I101" s="36" t="n"/>
+      <c r="J101" s="36" t="n"/>
+      <c r="K101" s="36" t="n"/>
+      <c r="L101" s="37">
         <f>IF($A101="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F101:$K101))</f>
         <v/>
       </c>
@@ -7843,15 +8009,15 @@
       <c r="A102" s="16" t="n"/>
       <c r="B102" s="16" t="n"/>
       <c r="C102" s="18" t="n"/>
-      <c r="D102" s="34" t="n"/>
-      <c r="E102" s="34" t="n"/>
-      <c r="F102" s="35" t="n"/>
-      <c r="G102" s="35" t="n"/>
-      <c r="H102" s="35" t="n"/>
-      <c r="I102" s="35" t="n"/>
-      <c r="J102" s="35" t="n"/>
-      <c r="K102" s="35" t="n"/>
-      <c r="L102" s="36">
+      <c r="D102" s="35" t="n"/>
+      <c r="E102" s="35" t="n"/>
+      <c r="F102" s="36" t="n"/>
+      <c r="G102" s="36" t="n"/>
+      <c r="H102" s="36" t="n"/>
+      <c r="I102" s="36" t="n"/>
+      <c r="J102" s="36" t="n"/>
+      <c r="K102" s="36" t="n"/>
+      <c r="L102" s="37">
         <f>IF($A102="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F102:$K102))</f>
         <v/>
       </c>
@@ -7888,15 +8054,15 @@
       <c r="A103" s="16" t="n"/>
       <c r="B103" s="16" t="n"/>
       <c r="C103" s="18" t="n"/>
-      <c r="D103" s="34" t="n"/>
-      <c r="E103" s="34" t="n"/>
-      <c r="F103" s="35" t="n"/>
-      <c r="G103" s="35" t="n"/>
-      <c r="H103" s="35" t="n"/>
-      <c r="I103" s="35" t="n"/>
-      <c r="J103" s="35" t="n"/>
-      <c r="K103" s="35" t="n"/>
-      <c r="L103" s="36">
+      <c r="D103" s="35" t="n"/>
+      <c r="E103" s="35" t="n"/>
+      <c r="F103" s="36" t="n"/>
+      <c r="G103" s="36" t="n"/>
+      <c r="H103" s="36" t="n"/>
+      <c r="I103" s="36" t="n"/>
+      <c r="J103" s="36" t="n"/>
+      <c r="K103" s="36" t="n"/>
+      <c r="L103" s="37">
         <f>IF($A103="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F103:$K103))</f>
         <v/>
       </c>
@@ -7933,15 +8099,15 @@
       <c r="A104" s="16" t="n"/>
       <c r="B104" s="16" t="n"/>
       <c r="C104" s="18" t="n"/>
-      <c r="D104" s="34" t="n"/>
-      <c r="E104" s="34" t="n"/>
-      <c r="F104" s="35" t="n"/>
-      <c r="G104" s="35" t="n"/>
-      <c r="H104" s="35" t="n"/>
-      <c r="I104" s="35" t="n"/>
-      <c r="J104" s="35" t="n"/>
-      <c r="K104" s="35" t="n"/>
-      <c r="L104" s="36">
+      <c r="D104" s="35" t="n"/>
+      <c r="E104" s="35" t="n"/>
+      <c r="F104" s="36" t="n"/>
+      <c r="G104" s="36" t="n"/>
+      <c r="H104" s="36" t="n"/>
+      <c r="I104" s="36" t="n"/>
+      <c r="J104" s="36" t="n"/>
+      <c r="K104" s="36" t="n"/>
+      <c r="L104" s="37">
         <f>IF($A104="","",SUMPRODUCT(($F$4:$K$4&lt;&gt;"")*$F104:$K104))</f>
         <v/>
       </c>
@@ -7984,31 +8150,31 @@
       <c r="C106" s="27" t="n"/>
       <c r="D106" s="27" t="n"/>
       <c r="E106" s="27" t="n"/>
-      <c r="F106" s="37">
+      <c r="F106" s="38">
         <f>SUM(F5:F104)</f>
         <v/>
       </c>
-      <c r="G106" s="37">
+      <c r="G106" s="38">
         <f>SUM(G5:G104)</f>
         <v/>
       </c>
-      <c r="H106" s="37">
+      <c r="H106" s="38">
         <f>SUM(H5:H104)</f>
         <v/>
       </c>
-      <c r="I106" s="37">
+      <c r="I106" s="38">
         <f>SUM(I5:I104)</f>
         <v/>
       </c>
-      <c r="J106" s="37">
+      <c r="J106" s="38">
         <f>SUM(J5:J104)</f>
         <v/>
       </c>
-      <c r="K106" s="37">
+      <c r="K106" s="38">
         <f>SUM(K5:K104)</f>
         <v/>
       </c>
-      <c r="L106" s="37">
+      <c r="L106" s="38">
         <f>SUM(L5:L104)</f>
         <v/>
       </c>
@@ -8150,27 +8316,27 @@
         </is>
       </c>
       <c r="B6" s="21">
-        <f>IF(B$5="","",予算割振!C$8)</f>
+        <f>IF(B$5="","",予算割振!D$8)</f>
         <v/>
       </c>
       <c r="C6" s="21">
-        <f>IF(C$5="","",予算割振!D$8)</f>
+        <f>IF(C$5="","",予算割振!E$8)</f>
         <v/>
       </c>
       <c r="D6" s="21">
-        <f>IF(D$5="","",予算割振!E$8)</f>
+        <f>IF(D$5="","",予算割振!F$8)</f>
         <v/>
       </c>
       <c r="E6" s="21">
-        <f>IF(E$5="","",予算割振!F$8)</f>
+        <f>IF(E$5="","",予算割振!G$8)</f>
         <v/>
       </c>
       <c r="F6" s="21">
-        <f>IF(F$5="","",予算割振!G$8)</f>
+        <f>IF(F$5="","",予算割振!H$8)</f>
         <v/>
       </c>
       <c r="G6" s="21">
-        <f>IF(G$5="","",予算割振!H$8)</f>
+        <f>IF(G$5="","",予算割振!I$8)</f>
         <v/>
       </c>
       <c r="H6" s="21">
@@ -8657,7 +8823,7 @@
           <t>時間</t>
         </is>
       </c>
-      <c r="B4" s="34" t="n">
+      <c r="B4" s="35" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8711,7 +8877,7 @@
         <f>設定!$B$21</f>
         <v/>
       </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="C8" s="35" t="n"/>
       <c r="D8" s="20">
         <f>IF($B8="","",$B$3*$B$4*$C8)</f>
         <v/>
@@ -8733,7 +8899,7 @@
         <f>設定!$B$22</f>
         <v/>
       </c>
-      <c r="C9" s="34" t="n"/>
+      <c r="C9" s="35" t="n"/>
       <c r="D9" s="20">
         <f>IF($B9="","",$B$3*$B$4*$C9)</f>
         <v/>
@@ -8755,7 +8921,7 @@
         <f>設定!$B$23</f>
         <v/>
       </c>
-      <c r="C10" s="34" t="n"/>
+      <c r="C10" s="35" t="n"/>
       <c r="D10" s="20">
         <f>IF($B10="","",$B$3*$B$4*$C10)</f>
         <v/>
@@ -8777,7 +8943,7 @@
         <f>設定!$B$24</f>
         <v/>
       </c>
-      <c r="C11" s="34" t="n"/>
+      <c r="C11" s="35" t="n"/>
       <c r="D11" s="20">
         <f>IF($B11="","",$B$3*$B$4*$C11)</f>
         <v/>
@@ -8799,7 +8965,7 @@
         <f>設定!$B$25</f>
         <v/>
       </c>
-      <c r="C12" s="34" t="n"/>
+      <c r="C12" s="35" t="n"/>
       <c r="D12" s="20">
         <f>IF($B12="","",$B$3*$B$4*$C12)</f>
         <v/>
@@ -8821,7 +8987,7 @@
         <f>設定!$B$26</f>
         <v/>
       </c>
-      <c r="C13" s="34" t="n"/>
+      <c r="C13" s="35" t="n"/>
       <c r="D13" s="20">
         <f>IF($B13="","",$B$3*$B$4*$C13)</f>
         <v/>
@@ -8842,7 +9008,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n"/>
-      <c r="C14" s="38">
+      <c r="C14" s="39">
         <f>SUM(C8:C13)</f>
         <v/>
       </c>
